--- a/Översikt FALKENBERG.xlsx
+++ b/Översikt FALKENBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46247</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>46253</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>46255</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45560</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>46255</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45741</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>46282</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>44592</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>44593</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>44516</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>44628</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>45079</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>45356</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>45527</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>45680</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45795</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>45335</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>44616</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>45600</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>45456</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>45356</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>44818</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44507</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>44460</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>44517</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>45196</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>44946</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>45600</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>45355</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>45667</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>45914</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>44926</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>45580</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>45561</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>44902</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>45565</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>45239</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>44972</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>46248</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>45273</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>45068</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45273</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>44964</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>45352</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>45352</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>45349</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>44705</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>45330</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>45945</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>46099</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>44806</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>44476</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>44607</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         <v>44553</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         <v>44539</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>44868</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>44461</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>44467</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>44867</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>44467</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>44466</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>44680</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>44600</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>44868</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>44816</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>44613</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>44689</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>44866</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>44616</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>44616</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>44617</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>44547</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>44599</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>44711</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>44879</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>44544</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>44600</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>44692</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>44692</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>44600</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>44539</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>44539</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>44747</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>44813</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>44841</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>44545</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>44719</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>44866</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         <v>44593</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>44467</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>44467</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>44467</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>44803</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>44614</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>44596</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>44685</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>44638</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>44539</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>44466</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>44628</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>44537</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>44481</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>44543</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>44539</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>44539</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>44958</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>45425</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>45363</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>44985</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>45552</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>45321</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>45205</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>45148</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>45546</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>45735</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>44946</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>44848</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>45736</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>45751</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>45419</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>45044</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>45147</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>44893</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>44600</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>45019</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>44576</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>45714</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>44903</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>44525</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>45714</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>44999</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>44986</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>45772</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>45300</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>45201</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>45001</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>45152</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>44545</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44946</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>44946</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>45435</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12927,7 +12927,7 @@
         <v>45127</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>45435</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         <v>45189</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>44986</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>45091</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>45595</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>44974</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45324</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>45182</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>45044</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>45575</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>45329</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>45188</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>45188</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>45548</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>44984</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>44689</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>45343</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>45462</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>45441</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>45682</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14470,7 +14470,7 @@
         <v>45682</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14543,7 +14543,7 @@
         <v>44974</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>45552</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14689,7 +14689,7 @@
         <v>45226</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>45252</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14835,7 +14835,7 @@
         <v>45435</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>45232</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>45481</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>44903</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>44882</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>45015</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>45219</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>44887</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>45182</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
         <v>44811</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>45350</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>45243</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>45272</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>45533</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>44910</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>45555</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>45681</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>45581</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>45673</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>45887</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>45800</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>44642</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>44687</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16514,7 +16514,7 @@
         <v>45770</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>45782</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>45582</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>45842</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
         <v>45764</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
         <v>45524</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         <v>45889</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>44644</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         <v>45552</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>45888</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>45280</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>45187</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17395,7 +17395,7 @@
         <v>45566</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17468,7 +17468,7 @@
         <v>45246</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17541,7 +17541,7 @@
         <v>45770</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17614,7 +17614,7 @@
         <v>44631</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17687,7 +17687,7 @@
         <v>44584</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17760,7 +17760,7 @@
         <v>45895</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         <v>45163</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17906,7 +17906,7 @@
         <v>45895</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17979,7 +17979,7 @@
         <v>44908</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18052,7 +18052,7 @@
         <v>45350</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>45195</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>45901</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45901</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>44946</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18417,7 +18417,7 @@
         <v>45546</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>45670</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>45390</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>45811</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>45908</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18787,7 +18787,7 @@
         <v>45691</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18860,7 +18860,7 @@
         <v>45914</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>45681</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>45917</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>45091</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>44977</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>45667</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19303,7 +19303,7 @@
         <v>45401</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>45923</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>45923</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>45923</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>45924</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>45926</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>45926</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>45926</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>45926</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
         <v>45202</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20038,7 +20038,7 @@
         <v>46142</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>46142</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20184,7 +20184,7 @@
         <v>45751</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44970</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>45931</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20403,7 +20403,7 @@
         <v>45931</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20476,7 +20476,7 @@
         <v>44963</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>44963</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>45931</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>45896</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>45896</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>45328</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>45937</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>45940</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>45618</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>45667</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21216,7 +21216,7 @@
         <v>45946</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         <v>45946</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         <v>44986</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>45946</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         <v>45951</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21581,7 +21581,7 @@
         <v>45377</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>45580</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>45950</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>45952</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>45952</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45953</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>45539</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45953</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>44957</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>45952</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>45954</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22389,7 +22389,7 @@
         <v>44543</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>45084</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
         <v>45959</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22608,7 +22608,7 @@
         <v>45959</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22681,7 +22681,7 @@
         <v>45959</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>45959</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>45950</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45547</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>45960</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23056,7 +23056,7 @@
         <v>45960</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>45960</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23207,7 +23207,7 @@
         <v>45961</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>45960</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>45965</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>45964</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23504,7 +23504,7 @@
         <v>45965</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         <v>45965</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>45414</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>45965</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>45965</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>45965</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>45965</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>45959</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>45965</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>45037</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>45959</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24317,7 +24317,7 @@
         <v>44622</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>44622</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>45635</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24536,7 +24536,7 @@
         <v>45968</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24609,7 +24609,7 @@
         <v>45350</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24682,7 +24682,7 @@
         <v>45971</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24755,7 +24755,7 @@
         <v>45971</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>45971</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>45968</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>45971</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>45973</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>45566</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25193,7 +25193,7 @@
         <v>45973</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25271,7 +25271,7 @@
         <v>44554</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25344,7 +25344,7 @@
         <v>45616</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>45975</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>45435</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         <v>45975</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>45644</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>45618</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>45300</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         <v>45456</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>45188</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>45667</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26084,7 +26084,7 @@
         <v>45705</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26157,7 +26157,7 @@
         <v>45933</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>44897</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26303,7 +26303,7 @@
         <v>45266</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26376,7 +26376,7 @@
         <v>45978</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26449,7 +26449,7 @@
         <v>45482</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>45988</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>45988</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>45323</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>45989</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>44610</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26897,7 +26897,7 @@
         <v>44740</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26970,7 +26970,7 @@
         <v>46162</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>45628</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>45048</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27194,7 +27194,7 @@
         <v>45566</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>45566</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27340,7 +27340,7 @@
         <v>45566</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27413,7 +27413,7 @@
         <v>45036</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27486,7 +27486,7 @@
         <v>44827</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>46162</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27632,7 +27632,7 @@
         <v>45999</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27705,7 +27705,7 @@
         <v>46164</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27778,7 +27778,7 @@
         <v>44831</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27851,7 +27851,7 @@
         <v>45138</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>45326</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>45681</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28070,7 +28070,7 @@
         <v>45751</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28143,7 +28143,7 @@
         <v>46003</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>44538</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         <v>46164</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>44740</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         <v>45667</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28513,7 +28513,7 @@
         <v>45189</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>44652</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>45686</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>46164</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>46166</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>46164</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28951,7 +28951,7 @@
         <v>46004</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>46006</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29097,7 +29097,7 @@
         <v>45741</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>44524</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>45678</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29316,7 +29316,7 @@
         <v>44574</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29389,7 +29389,7 @@
         <v>44900</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29462,7 +29462,7 @@
         <v>45601</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29535,7 +29535,7 @@
         <v>45953</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>44986</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>45923</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29754,7 +29754,7 @@
         <v>45714</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>45391</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>46168</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29973,7 +29973,7 @@
         <v>45300</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>46170</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30119,7 +30119,7 @@
         <v>45068</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>45188</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>46035</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>45349</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>45174</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>45624</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30557,7 +30557,7 @@
         <v>45401</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>45055</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>45055</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>46037</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30859,7 +30859,7 @@
         <v>46037</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>44656</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31005,7 +31005,7 @@
         <v>44664</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>46041</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31151,7 +31151,7 @@
         <v>46042</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31224,7 +31224,7 @@
         <v>45274</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
         <v>46045</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31370,7 +31370,7 @@
         <v>46172</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>44846</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31516,7 +31516,7 @@
         <v>46049</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31589,7 +31589,7 @@
         <v>45643</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31667,7 +31667,7 @@
         <v>45345</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31740,7 +31740,7 @@
         <v>46055</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>45119</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>45266</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>46052</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32032,7 +32032,7 @@
         <v>46007</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32105,7 +32105,7 @@
         <v>45966</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32178,7 +32178,7 @@
         <v>44916</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32251,7 +32251,7 @@
         <v>46178</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32324,7 +32324,7 @@
         <v>45474</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>46065</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>46182</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>44946</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>45058</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>46069</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>46182</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32835,7 +32835,7 @@
         <v>46070</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>44545</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>46184</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33054,7 +33054,7 @@
         <v>46065</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>45679</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>46077</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>45384</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33351,7 +33351,7 @@
         <v>46077</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>44938</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33497,7 +33497,7 @@
         <v>46082</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33570,7 +33570,7 @@
         <v>45187</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>46184</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>45131</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33789,7 +33789,7 @@
         <v>46082</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>45105</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>44806</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>45211</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34081,7 +34081,7 @@
         <v>46087</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34154,7 +34154,7 @@
         <v>45554</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
         <v>45377</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
         <v>45400</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34373,7 +34373,7 @@
         <v>46190</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>45239</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>45219</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34592,7 +34592,7 @@
         <v>45762</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>45244</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34738,7 +34738,7 @@
         <v>44692</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34811,7 +34811,7 @@
         <v>44806</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34884,7 +34884,7 @@
         <v>45212</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34957,7 +34957,7 @@
         <v>45212</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35030,7 +35030,7 @@
         <v>46097</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35103,7 +35103,7 @@
         <v>46099</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35176,7 +35176,7 @@
         <v>45426</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>45174</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>46196</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>46106</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>46106</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35541,7 +35541,7 @@
         <v>45351</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35614,7 +35614,7 @@
         <v>46106</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35687,7 +35687,7 @@
         <v>44467</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
         <v>45273</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35833,7 +35833,7 @@
         <v>45580</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35906,7 +35906,7 @@
         <v>44602</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>45575</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36052,7 +36052,7 @@
         <v>45627</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>46202</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>45474</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36271,7 +36271,7 @@
         <v>45181</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36344,7 +36344,7 @@
         <v>46202</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>46202</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>46120</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>45118</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>45247</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>46200</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36797,7 +36797,7 @@
         <v>45601</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36870,7 +36870,7 @@
         <v>45300</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36943,7 +36943,7 @@
         <v>45300</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>45245</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37089,7 +37089,7 @@
         <v>46244</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37162,7 +37162,7 @@
         <v>46127</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>44785</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37308,7 +37308,7 @@
         <v>45182</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37381,7 +37381,7 @@
         <v>45702</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>45252</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37527,7 +37527,7 @@
         <v>45629</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>45239</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>46203</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37746,7 +37746,7 @@
         <v>45272</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37819,7 +37819,7 @@
         <v>44469</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37892,7 +37892,7 @@
         <v>45561</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37965,7 +37965,7 @@
         <v>45831</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38038,7 +38038,7 @@
         <v>45029</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38111,7 +38111,7 @@
         <v>45680</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>45709</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38257,7 +38257,7 @@
         <v>45190</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38330,7 +38330,7 @@
         <v>45856</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38403,7 +38403,7 @@
         <v>45363</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38476,7 +38476,7 @@
         <v>46203</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38549,7 +38549,7 @@
         <v>44966</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38622,7 +38622,7 @@
         <v>45238</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38695,7 +38695,7 @@
         <v>45597</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>45560</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38846,7 +38846,7 @@
         <v>45357</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>45323</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>46251</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39065,7 +39065,7 @@
         <v>45381</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39138,7 +39138,7 @@
         <v>45127</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39216,7 +39216,7 @@
         <v>46248</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45229</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39362,7 +39362,7 @@
         <v>45282</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39435,7 +39435,7 @@
         <v>45142</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39508,7 +39508,7 @@
         <v>45035</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>44938</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39654,7 +39654,7 @@
         <v>45120</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>46253</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39800,7 +39800,7 @@
         <v>45664</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39873,7 +39873,7 @@
         <v>44627</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39946,7 +39946,7 @@
         <v>45001</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>44910</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>44957</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40165,7 +40165,7 @@
         <v>45246</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40238,7 +40238,7 @@
         <v>44827</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40311,7 +40311,7 @@
         <v>45435</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40384,7 +40384,7 @@
         <v>46212</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40457,7 +40457,7 @@
         <v>46212</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>46211</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40603,7 +40603,7 @@
         <v>46259</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40676,7 +40676,7 @@
         <v>45342</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>45714</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40827,7 +40827,7 @@
         <v>46259</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40900,7 +40900,7 @@
         <v>46258</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40973,7 +40973,7 @@
         <v>46259</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>45618</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>44694</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41192,7 +41192,7 @@
         <v>45588</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>45076</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41338,7 +41338,7 @@
         <v>44517</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>44852</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41484,7 +41484,7 @@
         <v>45131</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>45357</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41630,7 +41630,7 @@
         <v>44627</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41703,7 +41703,7 @@
         <v>45357</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>45226</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41849,7 +41849,7 @@
         <v>46217</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>44974</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>46260</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42068,7 +42068,7 @@
         <v>44964</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42141,7 +42141,7 @@
         <v>46263</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42214,7 +42214,7 @@
         <v>45355</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42287,7 +42287,7 @@
         <v>45117</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42360,7 +42360,7 @@
         <v>44946</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         <v>45439</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42506,7 +42506,7 @@
         <v>46263</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42579,7 +42579,7 @@
         <v>45175</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>45174</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42725,7 +42725,7 @@
         <v>45174</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45328</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42876,7 +42876,7 @@
         <v>45035</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42949,7 +42949,7 @@
         <v>46225</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43022,7 +43022,7 @@
         <v>45582</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43095,7 +43095,7 @@
         <v>45071</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>45777</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43241,7 +43241,7 @@
         <v>46271</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43314,7 +43314,7 @@
         <v>46271</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>46272</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43460,7 +43460,7 @@
         <v>45782</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43533,7 +43533,7 @@
         <v>46272</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43606,7 +43606,7 @@
         <v>45278</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45785</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43752,7 +43752,7 @@
         <v>45741</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43825,7 +43825,7 @@
         <v>45562</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>45443</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>45582</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44044,7 +44044,7 @@
         <v>45616</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44117,7 +44117,7 @@
         <v>46281</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44190,7 +44190,7 @@
         <v>45790</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44263,7 +44263,7 @@
         <v>46087</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44336,7 +44336,7 @@
         <v>46282</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>45748</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44482,7 +44482,7 @@
         <v>45686</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44555,7 +44555,7 @@
         <v>46282</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44628,7 +44628,7 @@
         <v>46282</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44701,7 +44701,7 @@
         <v>45666</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44774,7 +44774,7 @@
         <v>46282</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44847,7 +44847,7 @@
         <v>46282</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44920,7 +44920,7 @@
         <v>45799</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>46204</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45066,7 +45066,7 @@
         <v>45799</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45139,7 +45139,7 @@
         <v>45799</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45810</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>45467</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>45712</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45431,7 +45431,7 @@
         <v>45630</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>45615</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45577,7 +45577,7 @@
         <v>45821</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>45834</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45723,7 +45723,7 @@
         <v>45834</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45796,7 +45796,7 @@
         <v>45834</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>45836</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45942,7 +45942,7 @@
         <v>45838</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46015,7 +46015,7 @@
         <v>45838</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>45838</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46161,7 +46161,7 @@
         <v>45838</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46234,7 +46234,7 @@
         <v>45838</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>45845</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>44984</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46453,7 +46453,7 @@
         <v>45848</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46526,7 +46526,7 @@
         <v>45750</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>45777</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46672,7 +46672,7 @@
         <v>45800</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46745,7 +46745,7 @@
         <v>45184</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45184</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46891,7 +46891,7 @@
         <v>45337</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46964,7 +46964,7 @@
         <v>45249</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47037,7 +47037,7 @@
         <v>44846</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47110,7 +47110,7 @@
         <v>44846</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>45840</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>45826</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>45422</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47412,7 +47412,7 @@
         <v>45184</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47485,7 +47485,7 @@
         <v>45013</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>45273</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47631,7 +47631,7 @@
         <v>45280</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47704,7 +47704,7 @@
         <v>44767</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47777,7 +47777,7 @@
         <v>45079</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47850,7 +47850,7 @@
         <v>45817</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47923,7 +47923,7 @@
         <v>44693</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47996,7 +47996,7 @@
         <v>45434</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48069,7 +48069,7 @@
         <v>45013</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48142,7 +48142,7 @@
         <v>45074</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48215,7 +48215,7 @@
         <v>44943</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48293,7 +48293,7 @@
         <v>44943</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48371,7 +48371,7 @@
         <v>44818</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48449,7 +48449,7 @@
         <v>44502</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48522,7 +48522,7 @@
         <v>45215</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48595,7 +48595,7 @@
         <v>44515</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48668,7 +48668,7 @@
         <v>45337</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48741,7 +48741,7 @@
         <v>45387</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48814,7 +48814,7 @@
         <v>45761</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48887,7 +48887,7 @@
         <v>45754</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48960,7 +48960,7 @@
         <v>45068</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49033,7 +49033,7 @@
         <v>44866</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49106,7 +49106,7 @@
         <v>45260</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>45422</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49257,7 +49257,7 @@
         <v>45271</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49330,7 +49330,7 @@
         <v>44521</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45243</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49476,7 +49476,7 @@
         <v>45250</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49549,7 +49549,7 @@
         <v>45248</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49627,7 +49627,7 @@
         <v>45249</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49700,7 +49700,7 @@
         <v>45270</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49773,7 +49773,7 @@
         <v>44952</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49846,7 +49846,7 @@
         <v>45422</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49924,7 +49924,7 @@
         <v>45229</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49997,7 +49997,7 @@
         <v>45249</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50070,7 +50070,7 @@
         <v>44952</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>45434</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50216,7 +50216,7 @@
         <v>45146</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50289,7 +50289,7 @@
         <v>45068</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50362,7 +50362,7 @@
         <v>45305</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>44574</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50513,7 +50513,7 @@
         <v>45259</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50586,7 +50586,7 @@
         <v>45352</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50659,7 +50659,7 @@
         <v>44608</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50732,7 +50732,7 @@
         <v>45261</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50805,7 +50805,7 @@
         <v>44636</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50878,7 +50878,7 @@
         <v>45370</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50951,7 +50951,7 @@
         <v>44489</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51029,7 +51029,7 @@
         <v>45356</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51102,7 +51102,7 @@
         <v>45330</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51175,7 +51175,7 @@
         <v>44466</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51248,7 +51248,7 @@
         <v>45349</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51321,7 +51321,7 @@
         <v>45352</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51394,7 +51394,7 @@
         <v>45435</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>45370</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51540,7 +51540,7 @@
         <v>44466</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51613,7 +51613,7 @@
         <v>45580</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51686,7 +51686,7 @@
         <v>45370</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51759,7 +51759,7 @@
         <v>45335</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51832,7 +51832,7 @@
         <v>45534</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>44967</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51978,7 +51978,7 @@
         <v>45352</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52051,7 +52051,7 @@
         <v>44489</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52129,7 +52129,7 @@
         <v>45744</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52202,7 +52202,7 @@
         <v>45744</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52275,7 +52275,7 @@
         <v>45750</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52348,7 +52348,7 @@
         <v>45756</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52421,7 +52421,7 @@
         <v>45715</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>45910</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52567,7 +52567,7 @@
         <v>46020</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52640,7 +52640,7 @@
         <v>46042</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52713,7 +52713,7 @@
         <v>46058</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52786,7 +52786,7 @@
         <v>46122</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52859,7 +52859,7 @@
         <v>46154</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52932,7 +52932,7 @@
         <v>46154</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53005,7 +53005,7 @@
         <v>46154</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53078,7 +53078,7 @@
         <v>46154</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53151,7 +53151,7 @@
         <v>46160</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53224,7 +53224,7 @@
         <v>46206</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53297,7 +53297,7 @@
         <v>46253</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>

--- a/Översikt FALKENBERG.xlsx
+++ b/Översikt FALKENBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46247</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>46253</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>46255</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45560</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>46255</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45741</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>46282</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>44592</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>44593</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>44628</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>44516</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>45079</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>45356</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>45527</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>45680</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45335</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>45795</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>44616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45600</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>45456</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44539</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>45356</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>44818</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44507</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>44517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>45565</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>45914</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>44946</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>44926</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>45355</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>45600</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44972</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>45273</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>45068</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>45273</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>46248</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>45239</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>44902</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>45561</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>45196</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>45667</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>44705</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>44964</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>45352</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>45352</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>45349</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>45330</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>45945</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>46099</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44806</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>44476</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>44607</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>44553</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>44539</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>44868</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44467</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44867</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44467</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>44466</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>44680</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>44600</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>44868</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>44816</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>44613</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>44689</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>44866</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>44616</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>44616</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44617</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>44547</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>44599</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>44711</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>44879</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>44544</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>44600</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>44692</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>44692</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>44600</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>44539</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>44539</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>44747</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>44813</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>44841</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>44545</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>44719</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>44866</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>44593</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>44467</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>44467</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>44467</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>44803</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>44614</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>44596</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         <v>44685</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>44638</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>44539</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>44466</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>44537</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>44628</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>44481</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>44543</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>44539</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>44539</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>45627</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>45705</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>45212</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>45174</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>45212</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>45377</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>45195</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>45400</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>45350</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>44806</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         <v>45363</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>45426</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>45229</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>45462</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>45435</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>45546</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>45419</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>44903</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
         <v>44938</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11388,7 +11388,7 @@
         <v>44467</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>45580</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11534,7 +11534,7 @@
         <v>45323</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         <v>45147</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>45953</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>45686</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>45244</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>45533</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11972,7 +11972,7 @@
         <v>45439</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>45666</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>44545</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>45748</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>45247</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>45274</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>45342</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>45300</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>45300</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>45300</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>44946</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>45441</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>45887</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>45888</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>44908</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13077,7 +13077,7 @@
         <v>45644</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>45782</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>45582</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>45800</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>46035</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>45889</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>46037</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>45799</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>45799</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         <v>46037</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         <v>45770</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>44602</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>45071</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>46042</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>44897</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>45895</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>45895</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>45329</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>45799</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>45524</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>44916</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>44576</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>46045</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>45901</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
         <v>44900</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>45901</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14980,7 +14980,7 @@
         <v>45670</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>46049</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>45908</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>46052</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>44584</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>45272</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>46055</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>45554</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>45966</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15637,7 +15637,7 @@
         <v>45349</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15710,7 +15710,7 @@
         <v>45914</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>45219</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>45917</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>45547</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>45350</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>45552</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>45355</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>44938</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>46065</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>45924</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
         <v>45923</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>46070</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>46069</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>45923</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>45923</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>45926</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>45926</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>45926</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         <v>45926</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>45555</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17170,7 +17170,7 @@
         <v>46077</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17243,7 +17243,7 @@
         <v>44600</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17316,7 +17316,7 @@
         <v>46082</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17389,7 +17389,7 @@
         <v>45931</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>45931</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>46065</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>45931</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>46082</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>44974</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
         <v>45246</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
         <v>45810</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17973,7 +17973,7 @@
         <v>45575</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         <v>46087</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18119,7 +18119,7 @@
         <v>45896</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>45896</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>44656</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         <v>44694</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>45937</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18489,7 +18489,7 @@
         <v>44610</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>46097</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>45940</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>45055</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>45055</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18854,7 +18854,7 @@
         <v>45575</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
         <v>46099</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>45273</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>45946</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>45946</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>45946</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19292,7 +19292,7 @@
         <v>45950</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>45741</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19443,7 +19443,7 @@
         <v>45952</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>46106</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>45951</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>45952</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>45952</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
         <v>46106</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>46106</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
         <v>45953</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>45953</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20100,7 +20100,7 @@
         <v>45266</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20173,7 +20173,7 @@
         <v>45954</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20246,7 +20246,7 @@
         <v>45581</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>45714</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>45959</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20465,7 +20465,7 @@
         <v>45950</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>45960</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>45959</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>45959</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>45959</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>45960</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20908,7 +20908,7 @@
         <v>45964</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>46120</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>45961</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21137,7 +21137,7 @@
         <v>44946</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         <v>45965</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>45965</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>45965</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>45965</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>45965</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>45965</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>45965</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>45965</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
         <v>45968</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21872,7 +21872,7 @@
         <v>46127</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>45968</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22018,7 +22018,7 @@
         <v>45971</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22091,7 +22091,7 @@
         <v>45667</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45971</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45971</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>45971</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45202</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>45467</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>45973</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>45058</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22685,7 +22685,7 @@
         <v>45015</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>45615</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>45712</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>45973</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>45975</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23055,7 +23055,7 @@
         <v>45084</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>45975</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23206,7 +23206,7 @@
         <v>44964</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>45474</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>44977</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>45770</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>45630</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45035</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45582</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>45978</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>45989</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45595</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45187</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45174</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45152</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>44986</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45831</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>45174</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>45174</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>45189</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>45390</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45764</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45856</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>45709</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>45999</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>44852</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>44524</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>45811</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>45714</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>46003</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>46006</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>46004</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>45736</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>45035</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>45842</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>45561</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>45751</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>45226</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>44827</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>45205</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>45201</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>45821</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>44740</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>44740</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45566</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>45245</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>44910</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>44910</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>46142</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>45068</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>45735</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>46142</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>45628</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>45232</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27027,7 +27027,7 @@
         <v>44893</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>45001</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>45751</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45834</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>45834</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>45119</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>45834</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>44882</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>45838</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>45838</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>45635</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>44469</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>45933</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45959</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45959</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>45456</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28195,7 +28195,7 @@
         <v>45838</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>44957</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28341,7 +28341,7 @@
         <v>45838</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>46162</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>45838</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>45482</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28633,7 +28633,7 @@
         <v>44538</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>45188</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>44966</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>46164</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28925,7 +28925,7 @@
         <v>46162</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28998,7 +28998,7 @@
         <v>45350</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>46164</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>45280</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29217,7 +29217,7 @@
         <v>44984</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29290,7 +29290,7 @@
         <v>45845</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29363,7 +29363,7 @@
         <v>46164</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29436,7 +29436,7 @@
         <v>44545</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>46164</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>45597</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>45117</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>45848</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>45923</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44999</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
         <v>46166</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>45131</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>45142</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>44574</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>46168</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>45239</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>45750</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>46172</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>45425</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>45474</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>46170</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         <v>44525</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>44543</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30901,7 +30901,7 @@
         <v>45800</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30974,7 +30974,7 @@
         <v>45019</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>44827</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
         <v>45138</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>46007</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>45777</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>44515</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>44974</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>44521</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>45422</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>45422</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31714,7 +31714,7 @@
         <v>46178</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31787,7 +31787,7 @@
         <v>45422</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>44848</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31938,7 +31938,7 @@
         <v>45566</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32011,7 +32011,7 @@
         <v>45566</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>45566</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32157,7 +32157,7 @@
         <v>44818</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32235,7 +32235,7 @@
         <v>46182</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32308,7 +32308,7 @@
         <v>45068</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32381,7 +32381,7 @@
         <v>44866</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32454,7 +32454,7 @@
         <v>45387</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>45105</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32600,7 +32600,7 @@
         <v>45434</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32673,7 +32673,7 @@
         <v>46182</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32746,7 +32746,7 @@
         <v>45048</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>45229</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32892,7 +32892,7 @@
         <v>45273</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32965,7 +32965,7 @@
         <v>45079</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>45305</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33111,7 +33111,7 @@
         <v>44693</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>44952</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33257,7 +33257,7 @@
         <v>45817</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33330,7 +33330,7 @@
         <v>45146</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33403,7 +33403,7 @@
         <v>45840</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33481,7 +33481,7 @@
         <v>45337</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>46184</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33627,7 +33627,7 @@
         <v>44952</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>45761</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33773,7 +33773,7 @@
         <v>45280</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>45148</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>45328</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>45337</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>45068</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34143,7 +34143,7 @@
         <v>45074</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>45270</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>45249</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>44846</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>45013</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34508,7 +34508,7 @@
         <v>44846</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>46184</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34654,7 +34654,7 @@
         <v>44986</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>45260</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34800,7 +34800,7 @@
         <v>45248</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34878,7 +34878,7 @@
         <v>45249</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34951,7 +34951,7 @@
         <v>45271</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35024,7 +35024,7 @@
         <v>45434</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35097,7 +35097,7 @@
         <v>45215</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35170,7 +35170,7 @@
         <v>44622</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35243,7 +35243,7 @@
         <v>44767</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35316,7 +35316,7 @@
         <v>45013</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>45754</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>44502</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>45826</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>45714</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35681,7 +35681,7 @@
         <v>45249</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>45250</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>45243</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>45481</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>44943</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36051,7 +36051,7 @@
         <v>44943</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>45184</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>45184</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>45184</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>46190</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36421,7 +36421,7 @@
         <v>45377</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36494,7 +36494,7 @@
         <v>45552</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>45678</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36640,7 +36640,7 @@
         <v>45401</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36718,7 +36718,7 @@
         <v>46196</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36791,7 +36791,7 @@
         <v>45714</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36864,7 +36864,7 @@
         <v>45588</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36937,7 +36937,7 @@
         <v>45667</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44644</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37083,7 +37083,7 @@
         <v>46200</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37156,7 +37156,7 @@
         <v>45190</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>44554</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>46203</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>46202</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37448,7 +37448,7 @@
         <v>46202</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>45601</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37599,7 +37599,7 @@
         <v>45435</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37672,7 +37672,7 @@
         <v>46202</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37750,7 +37750,7 @@
         <v>46203</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37823,7 +37823,7 @@
         <v>45618</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37896,7 +37896,7 @@
         <v>45643</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>46251</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>45182</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38120,7 +38120,7 @@
         <v>45751</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>45187</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38266,7 +38266,7 @@
         <v>46253</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>46211</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45401</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>46258</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38563,7 +38563,7 @@
         <v>45435</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>46212</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38709,7 +38709,7 @@
         <v>46212</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>46259</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>45414</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>46217</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>44811</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>46260</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>46259</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>45188</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45181</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39371,7 +39371,7 @@
         <v>46259</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>44664</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>45680</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>45679</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>45163</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39741,7 +39741,7 @@
         <v>45182</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>45188</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39887,7 +39887,7 @@
         <v>45131</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>45239</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>45300</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
         <v>46263</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>46263</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>46225</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>45328</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40403,7 +40403,7 @@
         <v>45762</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>45343</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40549,7 +40549,7 @@
         <v>46272</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
         <v>44627</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40695,7 +40695,7 @@
         <v>46271</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40768,7 +40768,7 @@
         <v>46271</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>46272</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40914,7 +40914,7 @@
         <v>45272</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>44958</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>45091</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>45118</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>45252</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>44785</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41357,7 +41357,7 @@
         <v>45282</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>44831</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41503,7 +41503,7 @@
         <v>45357</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41576,7 +41576,7 @@
         <v>45091</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45539</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41722,7 +41722,7 @@
         <v>45238</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41795,7 +41795,7 @@
         <v>45691</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41868,7 +41868,7 @@
         <v>44946</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>46204</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42014,7 +42014,7 @@
         <v>46282</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>45044</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>46282</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>46281</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42306,7 +42306,7 @@
         <v>46282</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42379,7 +42379,7 @@
         <v>46282</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
         <v>46087</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42525,7 +42525,7 @@
         <v>45618</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42598,7 +42598,7 @@
         <v>45618</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42671,7 +42671,7 @@
         <v>46244</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42744,7 +42744,7 @@
         <v>45326</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>44946</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>44627</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>44887</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43036,7 +43036,7 @@
         <v>44692</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43109,7 +43109,7 @@
         <v>45560</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43182,7 +43182,7 @@
         <v>45211</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43255,7 +43255,7 @@
         <v>45175</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43328,7 +43328,7 @@
         <v>44970</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43401,7 +43401,7 @@
         <v>46041</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43474,7 +43474,7 @@
         <v>45580</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43547,7 +43547,7 @@
         <v>45345</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43620,7 +43620,7 @@
         <v>45189</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43693,7 +43693,7 @@
         <v>44946</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43766,7 +43766,7 @@
         <v>44946</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43839,7 +43839,7 @@
         <v>45357</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43912,7 +43912,7 @@
         <v>46248</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43985,7 +43985,7 @@
         <v>46290</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44058,7 +44058,7 @@
         <v>44974</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>46289</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>45566</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>44806</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44350,7 +44350,7 @@
         <v>44517</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44423,7 +44423,7 @@
         <v>45188</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44496,7 +44496,7 @@
         <v>45182</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         <v>46282</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44642,7 +44642,7 @@
         <v>45772</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44715,7 +44715,7 @@
         <v>45391</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44788,7 +44788,7 @@
         <v>45381</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44861,7 +44861,7 @@
         <v>45384</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44934,7 +44934,7 @@
         <v>45363</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
         <v>45036</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45080,7 +45080,7 @@
         <v>45435</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45153,7 +45153,7 @@
         <v>44984</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>45435</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45299,7 +45299,7 @@
         <v>45076</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45372,7 +45372,7 @@
         <v>45546</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45450,7 +45450,7 @@
         <v>45252</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45523,7 +45523,7 @@
         <v>45601</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45596,7 +45596,7 @@
         <v>45323</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45669,7 +45669,7 @@
         <v>45624</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45742,7 +45742,7 @@
         <v>44652</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45815,7 +45815,7 @@
         <v>45681</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45888,7 +45888,7 @@
         <v>45682</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45961,7 +45961,7 @@
         <v>45682</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46034,7 +46034,7 @@
         <v>45246</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         <v>45673</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>45321</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46253,7 +46253,7 @@
         <v>45357</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46326,7 +46326,7 @@
         <v>45127</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46404,7 +46404,7 @@
         <v>44985</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46477,7 +46477,7 @@
         <v>45548</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46550,7 +46550,7 @@
         <v>45044</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46623,7 +46623,7 @@
         <v>44631</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46696,7 +46696,7 @@
         <v>44689</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>44687</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46842,7 +46842,7 @@
         <v>45702</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46915,7 +46915,7 @@
         <v>45266</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>45664</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47061,7 +47061,7 @@
         <v>45629</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47134,7 +47134,7 @@
         <v>44642</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47207,7 +47207,7 @@
         <v>45686</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47280,7 +47280,7 @@
         <v>45552</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45351</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47426,7 +47426,7 @@
         <v>44846</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47499,7 +47499,7 @@
         <v>45324</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47572,7 +47572,7 @@
         <v>45243</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47645,7 +47645,7 @@
         <v>45120</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47718,7 +47718,7 @@
         <v>45037</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>44986</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45681</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47937,7 +47937,7 @@
         <v>44963</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48010,7 +48010,7 @@
         <v>44963</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>44903</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45219</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>44957</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48302,7 +48302,7 @@
         <v>45029</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48375,7 +48375,7 @@
         <v>44986</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>45001</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48521,7 +48521,7 @@
         <v>45616</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48594,7 +48594,7 @@
         <v>45667</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>45127</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>45226</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48818,7 +48818,7 @@
         <v>45681</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48891,7 +48891,7 @@
         <v>45300</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48964,7 +48964,7 @@
         <v>44622</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>45667</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>45777</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49183,7 +49183,7 @@
         <v>45782</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49256,7 +49256,7 @@
         <v>45278</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45785</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49402,7 +49402,7 @@
         <v>45741</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49475,7 +49475,7 @@
         <v>45443</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>45790</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49621,7 +49621,7 @@
         <v>45562</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49694,7 +49694,7 @@
         <v>45582</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>45616</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49840,7 +49840,7 @@
         <v>44574</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49918,7 +49918,7 @@
         <v>44608</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49991,7 +49991,7 @@
         <v>44636</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50064,7 +50064,7 @@
         <v>45259</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50137,7 +50137,7 @@
         <v>45352</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50210,7 +50210,7 @@
         <v>45261</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50283,7 +50283,7 @@
         <v>45370</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50356,7 +50356,7 @@
         <v>44489</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50434,7 +50434,7 @@
         <v>45356</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>45330</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>44466</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50653,7 +50653,7 @@
         <v>45349</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50726,7 +50726,7 @@
         <v>45352</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50799,7 +50799,7 @@
         <v>45435</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50872,7 +50872,7 @@
         <v>45370</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50945,7 +50945,7 @@
         <v>44466</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51018,7 +51018,7 @@
         <v>45580</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51091,7 +51091,7 @@
         <v>45370</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45335</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51237,7 +51237,7 @@
         <v>45534</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51310,7 +51310,7 @@
         <v>44967</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51383,7 +51383,7 @@
         <v>45352</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51456,7 +51456,7 @@
         <v>44489</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>45744</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>45744</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51680,7 +51680,7 @@
         <v>45750</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>45756</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>45715</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51899,7 +51899,7 @@
         <v>45910</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51972,7 +51972,7 @@
         <v>46020</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52045,7 +52045,7 @@
         <v>46042</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52118,7 +52118,7 @@
         <v>46058</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         <v>46122</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52264,7 +52264,7 @@
         <v>46154</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>46154</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52410,7 +52410,7 @@
         <v>46154</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52483,7 +52483,7 @@
         <v>46154</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52556,7 +52556,7 @@
         <v>46160</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52629,7 +52629,7 @@
         <v>46206</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52702,7 +52702,7 @@
         <v>46253</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>

--- a/Översikt FALKENBERG.xlsx
+++ b/Översikt FALKENBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46247</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>46253</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>46255</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45560</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>46255</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45741</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>46282</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>44592</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>44593</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>44628</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>44516</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>45079</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>45356</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>45527</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>45680</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45335</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>45795</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>44616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45600</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>45456</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44539</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>45356</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>44818</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44507</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>44517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>45565</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>45914</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>44946</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>44926</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>45355</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>45600</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44972</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>45273</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>45068</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>45273</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>46248</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>45239</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>44902</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>45561</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>45196</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>45667</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>44705</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>44964</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>45352</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>45352</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>45349</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>45330</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>45945</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>46099</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44806</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>44476</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>44607</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>44553</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>44539</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>44868</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44467</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44867</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44467</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>44466</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>44680</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>44600</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>44868</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>44816</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>44613</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>44689</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>44866</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>44616</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>44616</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44617</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>44547</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>44599</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>44711</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>44879</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>44544</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>44600</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>44692</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>44692</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>44600</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>44539</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>44539</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>44747</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>44813</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>44841</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>44545</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>44719</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>44866</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>44593</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>44467</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>44467</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>44467</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>44803</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>44614</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>44596</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         <v>44685</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>44638</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>44539</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>44466</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>44537</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>44628</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>44481</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>44543</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>44539</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>44539</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>45627</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>45705</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>45212</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>45174</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>45212</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>45377</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>45195</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>45400</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>45350</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>44806</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         <v>45363</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>45426</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>45229</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>45462</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>45435</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>45546</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>45419</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>44903</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
         <v>44938</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11388,7 +11388,7 @@
         <v>44467</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>45580</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11534,7 +11534,7 @@
         <v>45323</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         <v>45147</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>45953</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>45686</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>45244</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>45533</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11972,7 +11972,7 @@
         <v>45439</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>45666</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>44545</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>45748</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>45247</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>45274</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>45342</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>45300</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>45300</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>45300</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>44946</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>45441</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>45887</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>45888</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>44908</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13077,7 +13077,7 @@
         <v>45644</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>45782</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>45582</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>45800</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>46035</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>45889</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>46037</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>45799</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>45799</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         <v>46037</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         <v>45770</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>44602</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>45071</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>46042</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>44897</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>45895</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>45895</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>45329</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>45799</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>45524</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>44916</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>44576</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>46045</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>45901</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
         <v>44900</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>45901</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14980,7 +14980,7 @@
         <v>45670</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>46049</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>45908</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>46052</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>44584</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>45272</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>46055</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>45554</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>45966</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15637,7 +15637,7 @@
         <v>45349</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15710,7 +15710,7 @@
         <v>45914</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>45219</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>45917</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>45547</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>45350</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>45552</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>45355</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>44938</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>46065</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>45924</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
         <v>45923</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>46070</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>46069</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>45923</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>45923</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>45926</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>45926</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>45926</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         <v>45926</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>45555</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17170,7 +17170,7 @@
         <v>46077</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17243,7 +17243,7 @@
         <v>44600</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17316,7 +17316,7 @@
         <v>46082</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17389,7 +17389,7 @@
         <v>45931</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>45931</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>46065</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>45931</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>46082</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>44974</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
         <v>45246</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
         <v>45810</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17973,7 +17973,7 @@
         <v>45575</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         <v>46087</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18119,7 +18119,7 @@
         <v>45896</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>45896</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>44656</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         <v>44694</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>45937</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18489,7 +18489,7 @@
         <v>44610</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>46097</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>45940</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>45055</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>45055</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18854,7 +18854,7 @@
         <v>45575</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
         <v>46099</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>45273</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>45946</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>45946</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>45946</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19292,7 +19292,7 @@
         <v>45950</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>45741</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19443,7 +19443,7 @@
         <v>45952</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>46106</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>45951</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>45952</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>45952</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
         <v>46106</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>46106</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
         <v>45953</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>45953</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20100,7 +20100,7 @@
         <v>45266</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20173,7 +20173,7 @@
         <v>45954</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20246,7 +20246,7 @@
         <v>45581</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>45714</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>45959</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20465,7 +20465,7 @@
         <v>45950</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>45960</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>45959</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>45959</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>45959</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>45960</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20908,7 +20908,7 @@
         <v>45964</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>46120</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>45961</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21137,7 +21137,7 @@
         <v>44946</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         <v>45965</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>45965</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>45965</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>45965</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>45965</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>45965</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>45965</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>45965</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
         <v>45968</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21872,7 +21872,7 @@
         <v>46127</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>45968</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22018,7 +22018,7 @@
         <v>45971</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22091,7 +22091,7 @@
         <v>45667</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45971</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45971</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>45971</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45202</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>45467</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>45973</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>45058</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22685,7 +22685,7 @@
         <v>45015</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>45615</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>45712</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>45973</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>45975</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23055,7 +23055,7 @@
         <v>45084</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>45975</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23206,7 +23206,7 @@
         <v>44964</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>45474</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>44977</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>45770</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>45630</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45035</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45582</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>45978</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>45989</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45595</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45187</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45174</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45152</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>44986</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45831</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>45174</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>45174</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>45189</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>45390</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45764</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45856</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>45709</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>45999</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>44852</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>44524</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>45811</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>45714</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>46003</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>46006</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>46004</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>45736</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>45035</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>45842</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>45561</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>45751</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>45226</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>44827</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>45205</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>45201</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>45821</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>44740</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>44740</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45566</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>45245</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>44910</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>44910</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>46142</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>45068</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>45735</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>46142</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>45628</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>45232</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27027,7 +27027,7 @@
         <v>44893</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>45001</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>45751</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45834</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>45834</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>45119</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>45834</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>44882</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>45838</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>45838</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>45635</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>44469</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>45933</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45959</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45959</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>45456</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28195,7 +28195,7 @@
         <v>45838</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>44957</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28341,7 +28341,7 @@
         <v>45838</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>46162</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>45838</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>45482</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28633,7 +28633,7 @@
         <v>44538</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>45188</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>44966</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>46164</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28925,7 +28925,7 @@
         <v>46162</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28998,7 +28998,7 @@
         <v>45350</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>46164</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>45280</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29217,7 +29217,7 @@
         <v>44984</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29290,7 +29290,7 @@
         <v>45845</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29363,7 +29363,7 @@
         <v>46164</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29436,7 +29436,7 @@
         <v>44545</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>46164</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>45597</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>45117</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>45848</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>45923</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44999</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
         <v>46166</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>45131</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>45142</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>44574</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>46168</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>45239</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>45750</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>46172</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>45425</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>45474</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>46170</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         <v>44525</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>44543</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30901,7 +30901,7 @@
         <v>45800</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30974,7 +30974,7 @@
         <v>45019</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>44827</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
         <v>45138</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>46007</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>45777</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>44515</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>44974</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>44521</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>45422</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>45422</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31714,7 +31714,7 @@
         <v>46178</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31787,7 +31787,7 @@
         <v>45422</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>44848</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31938,7 +31938,7 @@
         <v>45566</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32011,7 +32011,7 @@
         <v>45566</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>45566</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32157,7 +32157,7 @@
         <v>44818</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32235,7 +32235,7 @@
         <v>46182</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32308,7 +32308,7 @@
         <v>45068</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32381,7 +32381,7 @@
         <v>44866</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32454,7 +32454,7 @@
         <v>45387</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>45105</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32600,7 +32600,7 @@
         <v>45434</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32673,7 +32673,7 @@
         <v>46182</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32746,7 +32746,7 @@
         <v>45048</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>45229</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32892,7 +32892,7 @@
         <v>45273</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32965,7 +32965,7 @@
         <v>45079</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>45305</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33111,7 +33111,7 @@
         <v>44693</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>44952</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33257,7 +33257,7 @@
         <v>45817</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33330,7 +33330,7 @@
         <v>45146</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33403,7 +33403,7 @@
         <v>45840</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33481,7 +33481,7 @@
         <v>45337</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>46184</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33627,7 +33627,7 @@
         <v>44952</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>45761</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33773,7 +33773,7 @@
         <v>45280</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>45148</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>45328</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>45337</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>45068</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34143,7 +34143,7 @@
         <v>45074</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>45270</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>45249</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>44846</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>45013</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34508,7 +34508,7 @@
         <v>44846</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>46184</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34654,7 +34654,7 @@
         <v>44986</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>45260</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34800,7 +34800,7 @@
         <v>45248</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34878,7 +34878,7 @@
         <v>45249</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34951,7 +34951,7 @@
         <v>45271</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35024,7 +35024,7 @@
         <v>45434</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35097,7 +35097,7 @@
         <v>45215</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35170,7 +35170,7 @@
         <v>44622</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35243,7 +35243,7 @@
         <v>44767</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35316,7 +35316,7 @@
         <v>45013</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>45754</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>44502</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>45826</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>45714</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35681,7 +35681,7 @@
         <v>45249</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>45250</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>45243</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>45481</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>44943</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36051,7 +36051,7 @@
         <v>44943</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>45184</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>45184</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>45184</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>46190</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36421,7 +36421,7 @@
         <v>45377</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36494,7 +36494,7 @@
         <v>45552</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>45678</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36640,7 +36640,7 @@
         <v>45401</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36718,7 +36718,7 @@
         <v>46196</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36791,7 +36791,7 @@
         <v>45714</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36864,7 +36864,7 @@
         <v>45588</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36937,7 +36937,7 @@
         <v>45667</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44644</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37083,7 +37083,7 @@
         <v>46200</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37156,7 +37156,7 @@
         <v>45190</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>44554</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>46203</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>46202</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37448,7 +37448,7 @@
         <v>46202</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>45601</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37599,7 +37599,7 @@
         <v>45435</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37672,7 +37672,7 @@
         <v>46202</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37750,7 +37750,7 @@
         <v>46203</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37823,7 +37823,7 @@
         <v>45618</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37896,7 +37896,7 @@
         <v>45643</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>46251</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>45182</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38120,7 +38120,7 @@
         <v>45751</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>45187</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38266,7 +38266,7 @@
         <v>46253</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>46211</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45401</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>46258</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38563,7 +38563,7 @@
         <v>45435</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>46212</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38709,7 +38709,7 @@
         <v>46212</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>46259</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>45414</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>46217</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>44811</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>46260</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>46259</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>45188</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45181</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39371,7 +39371,7 @@
         <v>46259</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>44664</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>45680</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>45679</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>45163</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39741,7 +39741,7 @@
         <v>45182</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>45188</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39887,7 +39887,7 @@
         <v>45131</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>45239</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>45300</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
         <v>46263</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>46263</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>46225</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>45328</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40403,7 +40403,7 @@
         <v>45762</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>45343</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40549,7 +40549,7 @@
         <v>46272</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
         <v>44627</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40695,7 +40695,7 @@
         <v>46271</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40768,7 +40768,7 @@
         <v>46271</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>46272</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40914,7 +40914,7 @@
         <v>45272</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>44958</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>45091</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>45118</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>45252</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>44785</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41357,7 +41357,7 @@
         <v>45282</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>44831</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41503,7 +41503,7 @@
         <v>45357</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41576,7 +41576,7 @@
         <v>45091</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45539</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41722,7 +41722,7 @@
         <v>45238</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41795,7 +41795,7 @@
         <v>45691</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41868,7 +41868,7 @@
         <v>44946</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>46204</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42014,7 +42014,7 @@
         <v>46282</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>45044</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>46282</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>46281</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42306,7 +42306,7 @@
         <v>46282</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42379,7 +42379,7 @@
         <v>46282</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
         <v>46087</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42525,7 +42525,7 @@
         <v>45618</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42598,7 +42598,7 @@
         <v>45618</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42671,7 +42671,7 @@
         <v>46244</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42744,7 +42744,7 @@
         <v>45326</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>44946</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>44627</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>44887</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43036,7 +43036,7 @@
         <v>44692</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43109,7 +43109,7 @@
         <v>45560</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43182,7 +43182,7 @@
         <v>45211</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43255,7 +43255,7 @@
         <v>45175</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43328,7 +43328,7 @@
         <v>44970</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43401,7 +43401,7 @@
         <v>46041</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43474,7 +43474,7 @@
         <v>45580</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43547,7 +43547,7 @@
         <v>45345</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43620,7 +43620,7 @@
         <v>45189</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43693,7 +43693,7 @@
         <v>44946</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43766,7 +43766,7 @@
         <v>44946</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43839,7 +43839,7 @@
         <v>45357</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43912,7 +43912,7 @@
         <v>46248</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43985,7 +43985,7 @@
         <v>46290</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44058,7 +44058,7 @@
         <v>44974</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>46289</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>45566</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>44806</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44350,7 +44350,7 @@
         <v>44517</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44423,7 +44423,7 @@
         <v>45188</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44496,7 +44496,7 @@
         <v>45182</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         <v>46282</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44642,7 +44642,7 @@
         <v>45772</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44715,7 +44715,7 @@
         <v>45391</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44788,7 +44788,7 @@
         <v>45381</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44861,7 +44861,7 @@
         <v>45384</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44934,7 +44934,7 @@
         <v>45363</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
         <v>45036</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45080,7 +45080,7 @@
         <v>45435</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45153,7 +45153,7 @@
         <v>44984</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>45435</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45299,7 +45299,7 @@
         <v>45076</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45372,7 +45372,7 @@
         <v>45546</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45450,7 +45450,7 @@
         <v>45252</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45523,7 +45523,7 @@
         <v>45601</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45596,7 +45596,7 @@
         <v>45323</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45669,7 +45669,7 @@
         <v>45624</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45742,7 +45742,7 @@
         <v>44652</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45815,7 +45815,7 @@
         <v>45681</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45888,7 +45888,7 @@
         <v>45682</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45961,7 +45961,7 @@
         <v>45682</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46034,7 +46034,7 @@
         <v>45246</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         <v>45673</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>45321</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46253,7 +46253,7 @@
         <v>45357</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46326,7 +46326,7 @@
         <v>45127</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46404,7 +46404,7 @@
         <v>44985</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46477,7 +46477,7 @@
         <v>45548</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46550,7 +46550,7 @@
         <v>45044</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46623,7 +46623,7 @@
         <v>44631</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46696,7 +46696,7 @@
         <v>44689</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>44687</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46842,7 +46842,7 @@
         <v>45702</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46915,7 +46915,7 @@
         <v>45266</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>45664</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47061,7 +47061,7 @@
         <v>45629</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47134,7 +47134,7 @@
         <v>44642</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47207,7 +47207,7 @@
         <v>45686</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47280,7 +47280,7 @@
         <v>45552</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45351</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47426,7 +47426,7 @@
         <v>44846</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47499,7 +47499,7 @@
         <v>45324</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47572,7 +47572,7 @@
         <v>45243</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47645,7 +47645,7 @@
         <v>45120</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47718,7 +47718,7 @@
         <v>45037</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>44986</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45681</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47937,7 +47937,7 @@
         <v>44963</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48010,7 +48010,7 @@
         <v>44963</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>44903</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45219</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>44957</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48302,7 +48302,7 @@
         <v>45029</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48375,7 +48375,7 @@
         <v>44986</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>45001</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48521,7 +48521,7 @@
         <v>45616</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48594,7 +48594,7 @@
         <v>45667</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>45127</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>45226</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48818,7 +48818,7 @@
         <v>45681</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48891,7 +48891,7 @@
         <v>45300</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48964,7 +48964,7 @@
         <v>44622</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>45667</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>45777</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49183,7 +49183,7 @@
         <v>45782</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49256,7 +49256,7 @@
         <v>45278</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45785</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49402,7 +49402,7 @@
         <v>45741</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49475,7 +49475,7 @@
         <v>45443</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>45790</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49621,7 +49621,7 @@
         <v>45562</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49694,7 +49694,7 @@
         <v>45582</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>45616</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49840,7 +49840,7 @@
         <v>44574</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49918,7 +49918,7 @@
         <v>44608</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49991,7 +49991,7 @@
         <v>44636</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50064,7 +50064,7 @@
         <v>45259</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50137,7 +50137,7 @@
         <v>45352</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50210,7 +50210,7 @@
         <v>45261</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50283,7 +50283,7 @@
         <v>45370</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50356,7 +50356,7 @@
         <v>44489</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50434,7 +50434,7 @@
         <v>45356</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>45330</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>44466</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50653,7 +50653,7 @@
         <v>45349</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50726,7 +50726,7 @@
         <v>45352</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50799,7 +50799,7 @@
         <v>45435</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50872,7 +50872,7 @@
         <v>45370</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50945,7 +50945,7 @@
         <v>44466</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51018,7 +51018,7 @@
         <v>45580</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51091,7 +51091,7 @@
         <v>45370</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45335</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51237,7 +51237,7 @@
         <v>45534</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51310,7 +51310,7 @@
         <v>44967</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51383,7 +51383,7 @@
         <v>45352</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51456,7 +51456,7 @@
         <v>44489</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>45744</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>45744</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51680,7 +51680,7 @@
         <v>45750</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>45756</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>45715</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51899,7 +51899,7 @@
         <v>45910</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51972,7 +51972,7 @@
         <v>46020</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52045,7 +52045,7 @@
         <v>46042</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52118,7 +52118,7 @@
         <v>46058</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         <v>46122</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52264,7 +52264,7 @@
         <v>46154</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>46154</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52410,7 +52410,7 @@
         <v>46154</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52483,7 +52483,7 @@
         <v>46154</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52556,7 +52556,7 @@
         <v>46160</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52629,7 +52629,7 @@
         <v>46206</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52702,7 +52702,7 @@
         <v>46253</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>

--- a/Översikt FALKENBERG.xlsx
+++ b/Översikt FALKENBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46247</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>46253</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>46255</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45560</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>46255</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45741</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>46282</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>44592</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>44593</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>44516</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>44628</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>45079</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>45356</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>45527</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>45680</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45795</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>45600</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>45335</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>45456</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>44539</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>44616</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>45356</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>44818</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44507</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>44517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>45196</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>44946</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>45600</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>45355</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>45914</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>45667</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>44926</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>45273</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>45068</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>45273</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>45561</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>44902</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>45565</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>45239</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>44972</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>46248</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>44964</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45352</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>45352</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45349</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>44705</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>45330</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>45945</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>46099</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44806</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>44607</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>44476</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>44553</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>44539</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>44868</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44867</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44680</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44600</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>44868</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>44816</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>44613</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>44689</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>44616</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>44866</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>44616</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44617</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>44547</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44599</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44711</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>44879</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>44544</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>44600</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>44692</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>44692</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>44600</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>44539</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>44539</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>44747</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>44813</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>44841</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>44545</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>44719</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>44866</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>44593</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>44803</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>44614</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>44596</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>44685</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>44638</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>44539</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>44628</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>44537</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>44481</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>44543</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>44539</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>44539</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>44958</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>45321</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>44985</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>44576</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>45425</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>45148</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>45552</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>45363</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>45546</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>45735</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>44946</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>45205</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>44848</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>45419</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>45147</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>44893</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>44600</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>45736</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>45751</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>45044</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>44908</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>45582</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>45019</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>46003</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45714</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>45616</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>45887</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>45800</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>46004</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>46006</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>44903</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>45782</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>45790</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>45953</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>44525</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>45582</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>45889</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>45888</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>45714</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>45772</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>45770</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>45300</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>44999</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>44986</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>45895</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>45895</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>46035</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>45901</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>45201</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>45901</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>45001</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>46037</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>44545</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>46037</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>45152</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>44946</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>44946</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>45670</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>45908</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>46042</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>45748</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>45686</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>46045</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>45666</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>45914</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>46049</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>45799</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>45917</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>45343</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>45441</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>45799</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>45799</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>44882</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>46055</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         <v>45435</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>45923</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>45923</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>45923</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>45127</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15287,7 +15287,7 @@
         <v>46052</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
         <v>45435</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>44986</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>45924</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>45189</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>45926</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15725,7 +15725,7 @@
         <v>45926</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>45926</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>45966</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>45926</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>45091</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>45595</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>45182</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>45044</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>45575</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>45931</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>45931</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>45329</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>45931</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>46065</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>45324</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>45548</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>45896</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>44689</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44974</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>45896</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>46069</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45188</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>45188</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>44984</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>46070</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>45937</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>45462</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45940</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>45682</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>45682</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>44974</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45946</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45810</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>45946</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>45946</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>46065</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>45226</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>45951</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>45552</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>45950</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>46077</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>45952</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>45952</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>45953</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>46082</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>45252</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>45953</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>45481</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>45952</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>45954</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19385,7 +19385,7 @@
         <v>46082</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>45435</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
         <v>45959</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>45959</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>45232</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>45959</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         <v>45959</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19896,7 +19896,7 @@
         <v>44903</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>46087</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>45950</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>45960</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>45961</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>45015</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>45960</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>45965</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>45964</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>45965</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20636,7 +20636,7 @@
         <v>45965</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>45965</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20782,7 +20782,7 @@
         <v>45965</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>45965</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20928,7 +20928,7 @@
         <v>45965</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>45965</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>45968</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>45971</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
         <v>45971</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>44887</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>45971</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21444,7 +21444,7 @@
         <v>45467</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21517,7 +21517,7 @@
         <v>45968</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         <v>46097</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>45219</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>45971</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21809,7 +21809,7 @@
         <v>45973</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
         <v>46099</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>44811</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22028,7 +22028,7 @@
         <v>45973</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         <v>45975</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>45350</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>45182</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>45975</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22408,7 +22408,7 @@
         <v>46106</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>45272</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>45712</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22627,7 +22627,7 @@
         <v>46106</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>46106</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>45243</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>45533</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>45630</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>45615</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         <v>44910</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>45555</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23211,7 +23211,7 @@
         <v>45581</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>45681</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>45821</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>45978</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>45673</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23576,7 +23576,7 @@
         <v>46120</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45989</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>44642</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>44687</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45999</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>46127</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45524</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>44644</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>45552</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45280</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>45187</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>45566</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>45834</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>45246</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45834</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>44631</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>45834</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>44584</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>45163</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45561</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>45831</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>45838</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>45838</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>45838</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>45838</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>45350</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>45838</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>45195</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>45709</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>45856</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>44946</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>45845</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>45546</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>44984</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>45770</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>45848</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>45691</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45681</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>45842</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>45764</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>45091</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>44977</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>45667</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>45401</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>45202</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>45750</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>45751</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>44970</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>45390</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>45811</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>44963</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>44963</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27397,7 +27397,7 @@
         <v>45328</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>45777</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>45800</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>45618</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>45184</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27767,7 +27767,7 @@
         <v>45184</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>45337</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27913,7 +27913,7 @@
         <v>45249</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>44846</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>44846</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>45840</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>45826</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28283,7 +28283,7 @@
         <v>45422</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>45184</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>45013</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28507,7 +28507,7 @@
         <v>45667</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28580,7 +28580,7 @@
         <v>45273</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28653,7 +28653,7 @@
         <v>44986</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28726,7 +28726,7 @@
         <v>45280</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28799,7 +28799,7 @@
         <v>44767</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>45079</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>45817</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29018,7 +29018,7 @@
         <v>44693</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29091,7 +29091,7 @@
         <v>45434</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29164,7 +29164,7 @@
         <v>45013</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29237,7 +29237,7 @@
         <v>45074</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29310,7 +29310,7 @@
         <v>44943</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>44943</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>46142</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>44818</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
         <v>46142</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>44502</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29763,7 +29763,7 @@
         <v>45215</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29836,7 +29836,7 @@
         <v>45377</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29909,7 +29909,7 @@
         <v>44515</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29982,7 +29982,7 @@
         <v>45580</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>45337</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>45387</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>45761</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>45754</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30347,7 +30347,7 @@
         <v>45539</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>44957</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30493,7 +30493,7 @@
         <v>45068</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30566,7 +30566,7 @@
         <v>44866</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30639,7 +30639,7 @@
         <v>44543</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30712,7 +30712,7 @@
         <v>45084</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>45260</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>45422</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>45271</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31009,7 +31009,7 @@
         <v>44521</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>45243</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31155,7 +31155,7 @@
         <v>45250</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>45248</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>45249</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>45270</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>44952</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>45422</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>45229</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31676,7 +31676,7 @@
         <v>45249</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31749,7 +31749,7 @@
         <v>44952</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>45434</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31895,7 +31895,7 @@
         <v>45146</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31968,7 +31968,7 @@
         <v>45068</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>45305</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32114,7 +32114,7 @@
         <v>45547</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32187,7 +32187,7 @@
         <v>45414</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32265,7 +32265,7 @@
         <v>45959</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>45959</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>45635</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>45037</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32557,7 +32557,7 @@
         <v>45933</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32630,7 +32630,7 @@
         <v>44622</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32703,7 +32703,7 @@
         <v>44622</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32776,7 +32776,7 @@
         <v>45350</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>45482</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>45566</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32995,7 +32995,7 @@
         <v>44554</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33068,7 +33068,7 @@
         <v>45616</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33141,7 +33141,7 @@
         <v>46162</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33214,7 +33214,7 @@
         <v>45435</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33287,7 +33287,7 @@
         <v>46162</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33360,7 +33360,7 @@
         <v>45644</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33433,7 +33433,7 @@
         <v>45618</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33506,7 +33506,7 @@
         <v>46164</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33579,7 +33579,7 @@
         <v>45300</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33652,7 +33652,7 @@
         <v>45456</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33725,7 +33725,7 @@
         <v>46164</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33798,7 +33798,7 @@
         <v>46164</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33871,7 +33871,7 @@
         <v>45188</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33944,7 +33944,7 @@
         <v>46166</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34017,7 +34017,7 @@
         <v>46164</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>45667</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34163,7 +34163,7 @@
         <v>45705</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34236,7 +34236,7 @@
         <v>44574</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34309,7 +34309,7 @@
         <v>44897</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34382,7 +34382,7 @@
         <v>45266</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34455,7 +34455,7 @@
         <v>45923</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34528,7 +34528,7 @@
         <v>46168</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>46170</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>45323</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34747,7 +34747,7 @@
         <v>44610</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34820,7 +34820,7 @@
         <v>46172</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34893,7 +34893,7 @@
         <v>44740</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34966,7 +34966,7 @@
         <v>46007</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35039,7 +35039,7 @@
         <v>45628</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35117,7 +35117,7 @@
         <v>46178</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>45048</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>46182</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>45566</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>45566</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>45566</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>46182</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>45036</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>44827</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35774,7 +35774,7 @@
         <v>46184</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35847,7 +35847,7 @@
         <v>46184</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>44831</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35993,7 +35993,7 @@
         <v>45138</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>45326</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>45681</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>45751</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>46190</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>44538</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>44740</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>45667</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>45189</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36655,7 +36655,7 @@
         <v>44652</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45686</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>45741</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>44524</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36947,7 +36947,7 @@
         <v>45678</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37020,7 +37020,7 @@
         <v>44900</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37093,7 +37093,7 @@
         <v>46196</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45601</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37239,7 +37239,7 @@
         <v>44986</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37312,7 +37312,7 @@
         <v>45714</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>45391</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37458,7 +37458,7 @@
         <v>46202</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>45300</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>46202</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>46202</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>46200</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>46203</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37906,7 +37906,7 @@
         <v>45068</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37979,7 +37979,7 @@
         <v>46203</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>45188</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>45349</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38198,7 +38198,7 @@
         <v>45174</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38271,7 +38271,7 @@
         <v>45624</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38344,7 +38344,7 @@
         <v>45401</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>45055</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>45055</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>44656</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>44664</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>46212</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>46212</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>45274</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>46211</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>46259</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>46259</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>44846</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>46258</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>46259</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39371,7 +39371,7 @@
         <v>45643</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>45345</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45119</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>45266</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>46217</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39741,7 +39741,7 @@
         <v>46260</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>46263</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39887,7 +39887,7 @@
         <v>44916</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>46263</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>45474</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
         <v>44946</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>45058</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>44545</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>46225</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>46271</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40471,7 +40471,7 @@
         <v>46271</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40544,7 +40544,7 @@
         <v>46272</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>46272</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>45679</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40768,7 +40768,7 @@
         <v>45384</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>44938</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40914,7 +40914,7 @@
         <v>45187</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>45131</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41060,7 +41060,7 @@
         <v>45105</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41133,7 +41133,7 @@
         <v>44806</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41206,7 +41206,7 @@
         <v>45211</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41279,7 +41279,7 @@
         <v>46281</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41352,7 +41352,7 @@
         <v>45554</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41425,7 +41425,7 @@
         <v>45377</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41498,7 +41498,7 @@
         <v>45400</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41571,7 +41571,7 @@
         <v>46282</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>45239</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41717,7 +41717,7 @@
         <v>45219</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41790,7 +41790,7 @@
         <v>45762</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>45244</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>44692</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42009,7 +42009,7 @@
         <v>46282</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42082,7 +42082,7 @@
         <v>46282</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42155,7 +42155,7 @@
         <v>46282</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>44806</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42301,7 +42301,7 @@
         <v>45212</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42374,7 +42374,7 @@
         <v>45212</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>46204</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42520,7 +42520,7 @@
         <v>45426</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42593,7 +42593,7 @@
         <v>45174</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>45351</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42739,7 +42739,7 @@
         <v>45273</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42812,7 +42812,7 @@
         <v>46041</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42885,7 +42885,7 @@
         <v>45580</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42958,7 +42958,7 @@
         <v>46087</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>44602</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45575</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43177,7 +43177,7 @@
         <v>45627</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43250,7 +43250,7 @@
         <v>46244</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>45474</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>45181</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43469,7 +43469,7 @@
         <v>46282</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43542,7 +43542,7 @@
         <v>45118</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>45247</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>45601</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43761,7 +43761,7 @@
         <v>45300</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45300</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43907,7 +43907,7 @@
         <v>45245</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
         <v>46293</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44053,7 +44053,7 @@
         <v>46293</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44126,7 +44126,7 @@
         <v>44785</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>46290</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44272,7 +44272,7 @@
         <v>46293</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44345,7 +44345,7 @@
         <v>45182</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44418,7 +44418,7 @@
         <v>45702</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44491,7 +44491,7 @@
         <v>45252</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44564,7 +44564,7 @@
         <v>46293</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>46248</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44710,7 +44710,7 @@
         <v>45629</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44783,7 +44783,7 @@
         <v>46289</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44856,7 +44856,7 @@
         <v>45239</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44929,7 +44929,7 @@
         <v>46293</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45002,7 +45002,7 @@
         <v>46293</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>45272</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45148,7 +45148,7 @@
         <v>46295</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45221,7 +45221,7 @@
         <v>46294</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45294,7 +45294,7 @@
         <v>45029</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45367,7 +45367,7 @@
         <v>45680</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>46251</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>45190</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45586,7 +45586,7 @@
         <v>45363</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45659,7 +45659,7 @@
         <v>44966</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45732,7 +45732,7 @@
         <v>45238</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45805,7 +45805,7 @@
         <v>45597</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45883,7 +45883,7 @@
         <v>45560</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45956,7 +45956,7 @@
         <v>45357</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46029,7 +46029,7 @@
         <v>45323</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46102,7 +46102,7 @@
         <v>46296</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
         <v>46253</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46248,7 +46248,7 @@
         <v>45381</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46321,7 +46321,7 @@
         <v>45127</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46399,7 +46399,7 @@
         <v>45229</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46472,7 +46472,7 @@
         <v>45282</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46545,7 +46545,7 @@
         <v>45142</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46618,7 +46618,7 @@
         <v>45035</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>44938</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46764,7 +46764,7 @@
         <v>45120</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45664</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46910,7 +46910,7 @@
         <v>44627</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46983,7 +46983,7 @@
         <v>45001</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>44910</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47129,7 +47129,7 @@
         <v>44957</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47202,7 +47202,7 @@
         <v>45246</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47275,7 +47275,7 @@
         <v>44827</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47348,7 +47348,7 @@
         <v>45435</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>45342</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47499,7 +47499,7 @@
         <v>45714</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47572,7 +47572,7 @@
         <v>45618</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47645,7 +47645,7 @@
         <v>44694</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47718,7 +47718,7 @@
         <v>45588</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>45076</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>44517</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47937,7 +47937,7 @@
         <v>44852</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48010,7 +48010,7 @@
         <v>45131</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>45357</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>44627</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>45357</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48302,7 +48302,7 @@
         <v>45226</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48375,7 +48375,7 @@
         <v>44974</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>44964</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48521,7 +48521,7 @@
         <v>45355</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48594,7 +48594,7 @@
         <v>45117</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>44946</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48740,7 +48740,7 @@
         <v>45439</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>45175</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48886,7 +48886,7 @@
         <v>45174</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48959,7 +48959,7 @@
         <v>45174</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49032,7 +49032,7 @@
         <v>45328</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>45035</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49183,7 +49183,7 @@
         <v>45582</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49256,7 +49256,7 @@
         <v>45071</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45777</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49402,7 +49402,7 @@
         <v>45782</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49475,7 +49475,7 @@
         <v>45278</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>45785</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49621,7 +49621,7 @@
         <v>45741</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49694,7 +49694,7 @@
         <v>45562</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>45443</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49840,7 +49840,7 @@
         <v>44574</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49918,7 +49918,7 @@
         <v>45259</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49991,7 +49991,7 @@
         <v>45352</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50064,7 +50064,7 @@
         <v>44608</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50137,7 +50137,7 @@
         <v>45261</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50210,7 +50210,7 @@
         <v>44636</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50283,7 +50283,7 @@
         <v>45370</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50356,7 +50356,7 @@
         <v>44489</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50434,7 +50434,7 @@
         <v>45356</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>45330</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>45349</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50653,7 +50653,7 @@
         <v>45352</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50726,7 +50726,7 @@
         <v>45435</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50799,7 +50799,7 @@
         <v>45370</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50872,7 +50872,7 @@
         <v>45580</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50945,7 +50945,7 @@
         <v>45370</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51018,7 +51018,7 @@
         <v>45335</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51091,7 +51091,7 @@
         <v>45534</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>44967</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51237,7 +51237,7 @@
         <v>45352</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51310,7 +51310,7 @@
         <v>44489</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51388,7 +51388,7 @@
         <v>45744</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51461,7 +51461,7 @@
         <v>45744</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>45750</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>45756</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51680,7 +51680,7 @@
         <v>45715</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>45910</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>46020</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51899,7 +51899,7 @@
         <v>46042</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51972,7 +51972,7 @@
         <v>46058</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52045,7 +52045,7 @@
         <v>46122</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52118,7 +52118,7 @@
         <v>46154</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         <v>46154</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52264,7 +52264,7 @@
         <v>46154</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>46154</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52410,7 +52410,7 @@
         <v>46160</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52483,7 +52483,7 @@
         <v>46206</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52556,7 +52556,7 @@
         <v>46253</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>

--- a/Översikt FALKENBERG.xlsx
+++ b/Översikt FALKENBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46247</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>46253</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>46255</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45560</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>46255</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45741</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>46282</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>44592</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>44593</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>44516</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>44628</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>45079</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>45356</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>45527</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>45680</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45795</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>45600</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>45335</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>45456</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>44539</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>44616</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>45356</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>44818</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44507</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>44517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>45196</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>44946</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>45600</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>45355</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>45914</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>45667</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>44926</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>45273</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>45068</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>45273</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>45561</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>44902</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>45565</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>45239</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>44972</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>46248</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>44964</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45352</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>45352</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45349</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>44705</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>45330</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>45945</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>46099</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44806</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>44607</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>44476</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>44553</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>44539</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>44868</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44867</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44680</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44600</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>44868</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>44816</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>44613</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>44689</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>44616</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>44866</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>44616</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44617</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>44547</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44599</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44711</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>44879</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>44544</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>44600</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>44692</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>44692</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>44600</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>44539</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>44539</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>44747</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>44813</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>44841</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>44545</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>44719</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>44866</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>44593</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>44803</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>44614</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>44596</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>44685</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>44638</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>44539</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>44628</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>44537</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>44481</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>44543</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>44539</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>44539</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>44958</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>45321</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>44985</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>44576</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>45425</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>45148</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>45552</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>45363</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>45546</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>45735</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>44946</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>45205</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>44848</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>45419</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>45147</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>44893</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>44600</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>45736</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>45751</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>45044</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>44908</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>45582</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>45019</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>46003</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45714</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>45616</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>45887</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>45800</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>46004</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>46006</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>44903</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>45782</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>45790</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>45953</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>44525</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>45582</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>45889</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>45888</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>45714</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>45772</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>45770</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>45300</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>44999</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>44986</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>45895</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>45895</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>46035</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>45901</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>45201</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>45901</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>45001</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>46037</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>44545</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>46037</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>45152</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>44946</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>44946</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>45670</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>45908</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>46042</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>45748</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>45686</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>46045</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>45666</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>45914</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>46049</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>45799</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>45917</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>45343</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>45441</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>45799</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>45799</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>44882</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>46055</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         <v>45435</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>45923</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>45923</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>45923</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>45127</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15287,7 +15287,7 @@
         <v>46052</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
         <v>45435</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>44986</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>45924</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>45189</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>45926</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15725,7 +15725,7 @@
         <v>45926</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>45926</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>45966</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>45926</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>45091</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>45595</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>45182</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>45044</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>45575</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>45931</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>45931</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>45329</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>45931</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>46065</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>45324</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>45548</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>45896</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>44689</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44974</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>45896</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>46069</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45188</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>45188</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>44984</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>46070</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>45937</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>45462</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45940</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>45682</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>45682</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>44974</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45946</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45810</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>45946</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>45946</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>46065</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>45226</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>45951</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>45552</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>45950</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>46077</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>45952</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>45952</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>45953</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>46082</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>45252</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>45953</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>45481</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>45952</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>45954</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19385,7 +19385,7 @@
         <v>46082</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>45435</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
         <v>45959</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>45959</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>45232</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>45959</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         <v>45959</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19896,7 +19896,7 @@
         <v>44903</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>46087</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>45950</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>45960</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>45961</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>45015</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>45960</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>45965</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>45964</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>45965</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20636,7 +20636,7 @@
         <v>45965</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>45965</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20782,7 +20782,7 @@
         <v>45965</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>45965</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20928,7 +20928,7 @@
         <v>45965</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>45965</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>45968</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>45971</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
         <v>45971</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>44887</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>45971</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21444,7 +21444,7 @@
         <v>45467</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21517,7 +21517,7 @@
         <v>45968</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         <v>46097</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>45219</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>45971</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21809,7 +21809,7 @@
         <v>45973</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
         <v>46099</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>44811</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22028,7 +22028,7 @@
         <v>45973</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         <v>45975</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>45350</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>45182</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>45975</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22408,7 +22408,7 @@
         <v>46106</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>45272</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>45712</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22627,7 +22627,7 @@
         <v>46106</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>46106</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>45243</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>45533</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>45630</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>45615</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         <v>44910</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>45555</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23211,7 +23211,7 @@
         <v>45581</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>45681</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>45821</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>45978</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>45673</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23576,7 +23576,7 @@
         <v>46120</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45989</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>44642</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>44687</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45999</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>46127</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45524</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>44644</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>45552</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45280</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>45187</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>45566</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>45834</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>45246</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45834</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>44631</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>45834</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>44584</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>45163</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45561</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>45831</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>45838</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>45838</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>45838</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>45838</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>45350</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>45838</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>45195</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>45709</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>45856</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>44946</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>45845</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>45546</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>44984</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>45770</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>45848</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>45691</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45681</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>45842</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>45764</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>45091</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>44977</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>45667</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>45401</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>45202</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>45750</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>45751</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>44970</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>45390</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>45811</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>44963</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>44963</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27397,7 +27397,7 @@
         <v>45328</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>45777</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>45800</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>45618</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>45184</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27767,7 +27767,7 @@
         <v>45184</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>45337</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27913,7 +27913,7 @@
         <v>45249</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>44846</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>44846</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>45840</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>45826</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28283,7 +28283,7 @@
         <v>45422</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>45184</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28434,7 +28434,7 @@
         <v>45013</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28507,7 +28507,7 @@
         <v>45667</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28580,7 +28580,7 @@
         <v>45273</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28653,7 +28653,7 @@
         <v>44986</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28726,7 +28726,7 @@
         <v>45280</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28799,7 +28799,7 @@
         <v>44767</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>45079</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>45817</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29018,7 +29018,7 @@
         <v>44693</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29091,7 +29091,7 @@
         <v>45434</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29164,7 +29164,7 @@
         <v>45013</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29237,7 +29237,7 @@
         <v>45074</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29310,7 +29310,7 @@
         <v>44943</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>44943</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>46142</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>44818</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
         <v>46142</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>44502</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29763,7 +29763,7 @@
         <v>45215</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29836,7 +29836,7 @@
         <v>45377</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29909,7 +29909,7 @@
         <v>44515</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29982,7 +29982,7 @@
         <v>45580</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>45337</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>45387</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>45761</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>45754</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30347,7 +30347,7 @@
         <v>45539</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>44957</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30493,7 +30493,7 @@
         <v>45068</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30566,7 +30566,7 @@
         <v>44866</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30639,7 +30639,7 @@
         <v>44543</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30712,7 +30712,7 @@
         <v>45084</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>45260</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>45422</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>45271</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31009,7 +31009,7 @@
         <v>44521</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>45243</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31155,7 +31155,7 @@
         <v>45250</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>45248</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>45249</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>45270</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>44952</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>45422</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>45229</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31676,7 +31676,7 @@
         <v>45249</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31749,7 +31749,7 @@
         <v>44952</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>45434</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31895,7 +31895,7 @@
         <v>45146</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31968,7 +31968,7 @@
         <v>45068</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32041,7 +32041,7 @@
         <v>45305</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32114,7 +32114,7 @@
         <v>45547</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32187,7 +32187,7 @@
         <v>45414</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32265,7 +32265,7 @@
         <v>45959</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>45959</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>45635</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>45037</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32557,7 +32557,7 @@
         <v>45933</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32630,7 +32630,7 @@
         <v>44622</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32703,7 +32703,7 @@
         <v>44622</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32776,7 +32776,7 @@
         <v>45350</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>45482</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>45566</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32995,7 +32995,7 @@
         <v>44554</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33068,7 +33068,7 @@
         <v>45616</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33141,7 +33141,7 @@
         <v>46162</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33214,7 +33214,7 @@
         <v>45435</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33287,7 +33287,7 @@
         <v>46162</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33360,7 +33360,7 @@
         <v>45644</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33433,7 +33433,7 @@
         <v>45618</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33506,7 +33506,7 @@
         <v>46164</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33579,7 +33579,7 @@
         <v>45300</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33652,7 +33652,7 @@
         <v>45456</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33725,7 +33725,7 @@
         <v>46164</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33798,7 +33798,7 @@
         <v>46164</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33871,7 +33871,7 @@
         <v>45188</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33944,7 +33944,7 @@
         <v>46166</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34017,7 +34017,7 @@
         <v>46164</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>45667</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34163,7 +34163,7 @@
         <v>45705</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34236,7 +34236,7 @@
         <v>44574</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34309,7 +34309,7 @@
         <v>44897</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34382,7 +34382,7 @@
         <v>45266</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34455,7 +34455,7 @@
         <v>45923</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34528,7 +34528,7 @@
         <v>46168</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>46170</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>45323</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34747,7 +34747,7 @@
         <v>44610</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34820,7 +34820,7 @@
         <v>46172</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34893,7 +34893,7 @@
         <v>44740</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34966,7 +34966,7 @@
         <v>46007</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35039,7 +35039,7 @@
         <v>45628</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35117,7 +35117,7 @@
         <v>46178</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>45048</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>46182</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>45566</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>45566</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>45566</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>46182</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>45036</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>44827</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35774,7 +35774,7 @@
         <v>46184</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35847,7 +35847,7 @@
         <v>46184</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>44831</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35993,7 +35993,7 @@
         <v>45138</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>45326</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>45681</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>45751</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>46190</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>44538</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>44740</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>45667</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>45189</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36655,7 +36655,7 @@
         <v>44652</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45686</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>45741</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>44524</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36947,7 +36947,7 @@
         <v>45678</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37020,7 +37020,7 @@
         <v>44900</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37093,7 +37093,7 @@
         <v>46196</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45601</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37239,7 +37239,7 @@
         <v>44986</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37312,7 +37312,7 @@
         <v>45714</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>45391</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37458,7 +37458,7 @@
         <v>46202</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>45300</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>46202</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>46202</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>46200</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>46203</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37906,7 +37906,7 @@
         <v>45068</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37979,7 +37979,7 @@
         <v>46203</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>45188</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>45349</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38198,7 +38198,7 @@
         <v>45174</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38271,7 +38271,7 @@
         <v>45624</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38344,7 +38344,7 @@
         <v>45401</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>45055</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>45055</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>44656</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>44664</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>46212</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>46212</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>45274</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>46211</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>46259</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>46259</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>44846</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>46258</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>46259</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39371,7 +39371,7 @@
         <v>45643</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>45345</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45119</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>45266</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>46217</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39741,7 +39741,7 @@
         <v>46260</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>46263</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39887,7 +39887,7 @@
         <v>44916</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>46263</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>45474</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
         <v>44946</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>45058</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>44545</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>46225</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>46271</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40471,7 +40471,7 @@
         <v>46271</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40544,7 +40544,7 @@
         <v>46272</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>46272</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>45679</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40768,7 +40768,7 @@
         <v>45384</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>44938</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40914,7 +40914,7 @@
         <v>45187</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>45131</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41060,7 +41060,7 @@
         <v>45105</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41133,7 +41133,7 @@
         <v>44806</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41206,7 +41206,7 @@
         <v>45211</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41279,7 +41279,7 @@
         <v>46281</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41352,7 +41352,7 @@
         <v>45554</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41425,7 +41425,7 @@
         <v>45377</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41498,7 +41498,7 @@
         <v>45400</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41571,7 +41571,7 @@
         <v>46282</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>45239</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41717,7 +41717,7 @@
         <v>45219</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41790,7 +41790,7 @@
         <v>45762</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>45244</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>44692</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42009,7 +42009,7 @@
         <v>46282</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42082,7 +42082,7 @@
         <v>46282</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42155,7 +42155,7 @@
         <v>46282</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>44806</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42301,7 +42301,7 @@
         <v>45212</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42374,7 +42374,7 @@
         <v>45212</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>46204</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42520,7 +42520,7 @@
         <v>45426</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42593,7 +42593,7 @@
         <v>45174</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>45351</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42739,7 +42739,7 @@
         <v>45273</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42812,7 +42812,7 @@
         <v>46041</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42885,7 +42885,7 @@
         <v>45580</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42958,7 +42958,7 @@
         <v>46087</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>44602</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45575</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43177,7 +43177,7 @@
         <v>45627</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43250,7 +43250,7 @@
         <v>46244</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>45474</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>45181</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43469,7 +43469,7 @@
         <v>46282</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43542,7 +43542,7 @@
         <v>45118</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>45247</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>45601</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43761,7 +43761,7 @@
         <v>45300</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45300</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43907,7 +43907,7 @@
         <v>45245</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
         <v>46293</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44053,7 +44053,7 @@
         <v>46293</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44126,7 +44126,7 @@
         <v>44785</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>46290</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44272,7 +44272,7 @@
         <v>46293</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44345,7 +44345,7 @@
         <v>45182</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44418,7 +44418,7 @@
         <v>45702</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44491,7 +44491,7 @@
         <v>45252</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44564,7 +44564,7 @@
         <v>46293</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>46248</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44710,7 +44710,7 @@
         <v>45629</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44783,7 +44783,7 @@
         <v>46289</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44856,7 +44856,7 @@
         <v>45239</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44929,7 +44929,7 @@
         <v>46293</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45002,7 +45002,7 @@
         <v>46293</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>45272</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45148,7 +45148,7 @@
         <v>46295</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45221,7 +45221,7 @@
         <v>46294</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45294,7 +45294,7 @@
         <v>45029</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45367,7 +45367,7 @@
         <v>45680</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>46251</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>45190</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45586,7 +45586,7 @@
         <v>45363</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45659,7 +45659,7 @@
         <v>44966</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45732,7 +45732,7 @@
         <v>45238</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45805,7 +45805,7 @@
         <v>45597</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45883,7 +45883,7 @@
         <v>45560</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45956,7 +45956,7 @@
         <v>45357</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46029,7 +46029,7 @@
         <v>45323</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46102,7 +46102,7 @@
         <v>46296</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
         <v>46253</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46248,7 +46248,7 @@
         <v>45381</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46321,7 +46321,7 @@
         <v>45127</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46399,7 +46399,7 @@
         <v>45229</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46472,7 +46472,7 @@
         <v>45282</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46545,7 +46545,7 @@
         <v>45142</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46618,7 +46618,7 @@
         <v>45035</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>44938</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46764,7 +46764,7 @@
         <v>45120</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45664</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46910,7 +46910,7 @@
         <v>44627</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46983,7 +46983,7 @@
         <v>45001</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>44910</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47129,7 +47129,7 @@
         <v>44957</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47202,7 +47202,7 @@
         <v>45246</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47275,7 +47275,7 @@
         <v>44827</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47348,7 +47348,7 @@
         <v>45435</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>45342</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47499,7 +47499,7 @@
         <v>45714</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47572,7 +47572,7 @@
         <v>45618</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47645,7 +47645,7 @@
         <v>44694</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47718,7 +47718,7 @@
         <v>45588</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>45076</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>44517</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47937,7 +47937,7 @@
         <v>44852</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48010,7 +48010,7 @@
         <v>45131</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>45357</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>44627</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>45357</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48302,7 +48302,7 @@
         <v>45226</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48375,7 +48375,7 @@
         <v>44974</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>44964</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48521,7 +48521,7 @@
         <v>45355</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48594,7 +48594,7 @@
         <v>45117</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>44946</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48740,7 +48740,7 @@
         <v>45439</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>45175</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48886,7 +48886,7 @@
         <v>45174</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48959,7 +48959,7 @@
         <v>45174</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49032,7 +49032,7 @@
         <v>45328</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>45035</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49183,7 +49183,7 @@
         <v>45582</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49256,7 +49256,7 @@
         <v>45071</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45777</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49402,7 +49402,7 @@
         <v>45782</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49475,7 +49475,7 @@
         <v>45278</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>45785</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49621,7 +49621,7 @@
         <v>45741</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49694,7 +49694,7 @@
         <v>45562</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>45443</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49840,7 +49840,7 @@
         <v>44574</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49918,7 +49918,7 @@
         <v>45259</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49991,7 +49991,7 @@
         <v>45352</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50064,7 +50064,7 @@
         <v>44608</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50137,7 +50137,7 @@
         <v>45261</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50210,7 +50210,7 @@
         <v>44636</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50283,7 +50283,7 @@
         <v>45370</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50356,7 +50356,7 @@
         <v>44489</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50434,7 +50434,7 @@
         <v>45356</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>45330</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>45349</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50653,7 +50653,7 @@
         <v>45352</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50726,7 +50726,7 @@
         <v>45435</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50799,7 +50799,7 @@
         <v>45370</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50872,7 +50872,7 @@
         <v>45580</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50945,7 +50945,7 @@
         <v>45370</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51018,7 +51018,7 @@
         <v>45335</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51091,7 +51091,7 @@
         <v>45534</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>44967</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51237,7 +51237,7 @@
         <v>45352</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51310,7 +51310,7 @@
         <v>44489</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51388,7 +51388,7 @@
         <v>45744</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51461,7 +51461,7 @@
         <v>45744</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>45750</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>45756</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51680,7 +51680,7 @@
         <v>45715</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>45910</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>46020</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51899,7 +51899,7 @@
         <v>46042</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51972,7 +51972,7 @@
         <v>46058</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52045,7 +52045,7 @@
         <v>46122</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52118,7 +52118,7 @@
         <v>46154</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         <v>46154</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52264,7 +52264,7 @@
         <v>46154</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>46154</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52410,7 +52410,7 @@
         <v>46160</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52483,7 +52483,7 @@
         <v>46206</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52556,7 +52556,7 @@
         <v>46253</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>

--- a/Översikt FALKENBERG.xlsx
+++ b/Översikt FALKENBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46247</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>46253</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>46255</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45560</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>46255</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45741</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>46282</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>44593</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>44592</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>44628</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>44516</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>45079</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>45356</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>45527</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>45680</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45335</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>45795</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>44616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45600</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>45456</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44539</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>45356</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>44818</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44507</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>44517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>45561</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>45565</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>44972</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>45196</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>45667</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>45914</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>44946</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>44926</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>45355</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>45600</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>45239</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>45273</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>45068</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>45273</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>44902</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>46248</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>44705</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>44964</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>45352</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>45352</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>45349</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>45330</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>45945</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>46099</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44806</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>44607</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>44553</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>44539</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>44868</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>44867</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44680</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44600</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44868</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>44816</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>44613</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>44689</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>44616</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>44616</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>44617</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>44547</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44599</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>44711</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44879</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44544</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>44539</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>44719</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>44803</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>44600</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>44537</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>44628</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>44692</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>44692</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>44614</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>44600</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>44596</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>44866</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>44685</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>44539</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>44539</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>44638</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>44747</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         <v>44593</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>44813</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>44841</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>44545</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>44481</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>44543</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>44539</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>45232</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>44652</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>44893</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>45001</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>45681</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>45682</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>45682</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>45246</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>45673</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>45363</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>44539</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>44806</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>45321</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>45751</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>45627</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>45357</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>45119</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>45127</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>45705</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>45350</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>44985</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>44882</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>45548</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>45212</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>45212</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>45044</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>44631</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>45456</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>44957</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>45377</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>45174</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         <v>45426</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>44689</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>45229</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         <v>45195</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>44687</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>45702</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>45266</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>45664</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>45629</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>44538</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>45188</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>45400</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>44966</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>45350</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>45546</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44642</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>45280</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>45462</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>45435</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>44545</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>45686</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>45552</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>44903</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>45351</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>45597</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>45117</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>44846</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>45419</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>45324</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>45243</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>44999</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>44938</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>45120</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>45131</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>45142</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>45323</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>45037</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>44986</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>45681</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>45580</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>45147</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>44963</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>44963</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>45244</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         <v>44903</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>45533</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>45439</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>45239</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>45888</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
         <v>45219</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44908</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>44545</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15340,7 +15340,7 @@
         <v>45247</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>45782</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>45274</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>45425</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         <v>45582</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
         <v>45342</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>45474</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>45300</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>45300</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>45300</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>44946</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>45800</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>44525</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>45889</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>44543</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
         <v>44957</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>45019</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>45029</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>45441</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>45770</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>44986</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>45895</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>45895</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>45001</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>45644</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>45616</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>45667</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>45901</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>45127</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>45901</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>45670</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44827</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>45226</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>45138</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
         <v>44602</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17910,7 +17910,7 @@
         <v>45071</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         <v>45681</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>44897</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>45329</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18202,7 +18202,7 @@
         <v>45524</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>44916</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>45908</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>45300</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>44576</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>44622</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>45667</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>44900</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>44974</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45777</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         <v>44848</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>45566</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>45566</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>45566</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>45782</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
         <v>45105</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>45048</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19443,7 +19443,7 @@
         <v>45278</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>45914</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44584</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>45148</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>45328</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>45272</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>45554</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>45917</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>45349</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>44986</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45219</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20251,7 +20251,7 @@
         <v>45785</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>44622</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>45547</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20470,7 +20470,7 @@
         <v>45714</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>45350</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>45924</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>45741</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>45443</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>45923</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20908,7 +20908,7 @@
         <v>45552</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>45355</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21054,7 +21054,7 @@
         <v>45481</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>44938</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>45790</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>45562</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21346,7 +21346,7 @@
         <v>45923</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21419,7 +21419,7 @@
         <v>45923</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>45582</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         <v>45377</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>45926</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>45926</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>45552</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>45926</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>45926</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>45678</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22076,7 +22076,7 @@
         <v>45616</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>45401</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>45555</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>45686</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>44600</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>45714</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>45666</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>45588</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22665,7 +22665,7 @@
         <v>45748</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>45931</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>45931</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>45931</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>44974</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>45246</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>45667</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>44644</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>45575</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
         <v>45190</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>44554</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>45601</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>44656</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>44694</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>45435</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>45799</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>45799</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>45799</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>45618</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>45896</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>44610</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>45896</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>45055</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>45055</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24417,7 +24417,7 @@
         <v>45575</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24490,7 +24490,7 @@
         <v>45273</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24563,7 +24563,7 @@
         <v>45643</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45937</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>45741</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         <v>45810</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>45182</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24938,7 +24938,7 @@
         <v>45751</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>45940</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>45187</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25157,7 +25157,7 @@
         <v>45946</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>45946</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>45946</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>45266</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>45467</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25522,7 +25522,7 @@
         <v>45615</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25595,7 +25595,7 @@
         <v>45401</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>45712</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25746,7 +25746,7 @@
         <v>45581</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25819,7 +25819,7 @@
         <v>45630</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>45714</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>45950</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26043,7 +26043,7 @@
         <v>45435</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>45821</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26189,7 +26189,7 @@
         <v>44946</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26262,7 +26262,7 @@
         <v>45952</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26335,7 +26335,7 @@
         <v>45414</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>44811</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>45188</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26559,7 +26559,7 @@
         <v>45181</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26632,7 +26632,7 @@
         <v>45951</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>45667</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>45952</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26856,7 +26856,7 @@
         <v>45952</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>45202</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27002,7 +27002,7 @@
         <v>45953</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27075,7 +27075,7 @@
         <v>45953</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27148,7 +27148,7 @@
         <v>45954</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>45959</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27294,7 +27294,7 @@
         <v>45950</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
         <v>45960</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>45959</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
         <v>45959</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>45959</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>45960</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>45834</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>45058</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>45834</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27956,7 +27956,7 @@
         <v>45015</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>44664</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>45964</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>45834</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>45084</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>45680</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28399,7 +28399,7 @@
         <v>45838</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>45838</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>45679</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28623,7 +28623,7 @@
         <v>44964</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>45838</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28769,7 +28769,7 @@
         <v>45474</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28842,7 +28842,7 @@
         <v>45838</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28915,7 +28915,7 @@
         <v>45961</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>45838</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>45965</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29134,7 +29134,7 @@
         <v>45163</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29207,7 +29207,7 @@
         <v>45182</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>45188</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29353,7 +29353,7 @@
         <v>45965</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29426,7 +29426,7 @@
         <v>45965</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>44977</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>45965</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>45965</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>45965</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>45965</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>45965</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>45968</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>45131</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>45968</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>45035</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         <v>45971</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>45239</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>45971</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>45971</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>45582</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>45300</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30677,7 +30677,7 @@
         <v>45971</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>44984</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>45845</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>45595</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>45973</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>45848</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
         <v>45187</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>45174</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>45973</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>45152</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>44986</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>45174</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>45174</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>45328</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>45189</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>45750</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>45762</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>45343</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>44852</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>45975</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>45800</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>44524</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>44627</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>45777</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>45714</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>44515</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>44521</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>45736</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>45422</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>45422</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32897,7 +32897,7 @@
         <v>45422</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32975,7 +32975,7 @@
         <v>44818</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33053,7 +33053,7 @@
         <v>45068</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33126,7 +33126,7 @@
         <v>44866</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>45387</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>45434</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>45229</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>45273</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33491,7 +33491,7 @@
         <v>45079</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>45305</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33637,7 +33637,7 @@
         <v>45035</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>44693</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>44952</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>45817</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>45146</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34002,7 +34002,7 @@
         <v>45840</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>45337</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>44952</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34226,7 +34226,7 @@
         <v>45761</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>45280</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34372,7 +34372,7 @@
         <v>45337</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34445,7 +34445,7 @@
         <v>45068</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34518,7 +34518,7 @@
         <v>45074</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         <v>45270</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34664,7 +34664,7 @@
         <v>45249</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>44846</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>45013</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>44846</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>45260</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35029,7 +35029,7 @@
         <v>45248</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35107,7 +35107,7 @@
         <v>45249</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35180,7 +35180,7 @@
         <v>45271</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35253,7 +35253,7 @@
         <v>45751</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35326,7 +35326,7 @@
         <v>45434</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>45215</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35472,7 +35472,7 @@
         <v>44767</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>45226</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35618,7 +35618,7 @@
         <v>45013</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         <v>45754</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>44502</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>45826</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35910,7 +35910,7 @@
         <v>45249</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35983,7 +35983,7 @@
         <v>45250</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>45243</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>44943</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>44943</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>45184</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>45184</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>45184</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>45272</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>44827</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36650,7 +36650,7 @@
         <v>44958</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45091</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>45118</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>45252</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36947,7 +36947,7 @@
         <v>44785</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37020,7 +37020,7 @@
         <v>45282</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37093,7 +37093,7 @@
         <v>44831</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45357</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37239,7 +37239,7 @@
         <v>45091</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37312,7 +37312,7 @@
         <v>45205</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>45201</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37463,7 +37463,7 @@
         <v>45539</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37536,7 +37536,7 @@
         <v>45238</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>45691</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>44946</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>44740</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37828,7 +37828,7 @@
         <v>44740</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37901,7 +37901,7 @@
         <v>46106</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>45566</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>45044</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38120,7 +38120,7 @@
         <v>45245</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>46106</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38266,7 +38266,7 @@
         <v>44910</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>44910</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45978</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         <v>45989</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38558,7 +38558,7 @@
         <v>45068</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38631,7 +38631,7 @@
         <v>45735</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45618</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38777,7 +38777,7 @@
         <v>45618</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38850,7 +38850,7 @@
         <v>45326</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38923,7 +38923,7 @@
         <v>45628</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>46120</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>44946</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>44627</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>45999</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>46127</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39371,7 +39371,7 @@
         <v>44887</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>44692</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>45560</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>45211</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39663,7 +39663,7 @@
         <v>45175</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>46003</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39809,7 +39809,7 @@
         <v>44970</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39882,7 +39882,7 @@
         <v>46006</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>46004</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40028,7 +40028,7 @@
         <v>45770</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
         <v>45580</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>45345</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>45189</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>44946</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>44946</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40471,7 +40471,7 @@
         <v>45357</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40544,7 +40544,7 @@
         <v>44974</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>45566</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>44806</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40763,7 +40763,7 @@
         <v>44517</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45188</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40909,7 +40909,7 @@
         <v>45182</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40982,7 +40982,7 @@
         <v>45772</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41055,7 +41055,7 @@
         <v>45831</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41128,7 +41128,7 @@
         <v>45391</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41201,7 +41201,7 @@
         <v>45953</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>45381</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41347,7 +41347,7 @@
         <v>45384</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41420,7 +41420,7 @@
         <v>45390</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>45764</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>45856</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>45709</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41712,7 +41712,7 @@
         <v>45363</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41785,7 +41785,7 @@
         <v>45036</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41858,7 +41858,7 @@
         <v>45811</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41931,7 +41931,7 @@
         <v>45435</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42004,7 +42004,7 @@
         <v>44984</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>45435</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42150,7 +42150,7 @@
         <v>45076</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42223,7 +42223,7 @@
         <v>45842</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>45561</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>46035</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42442,7 +42442,7 @@
         <v>46037</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42520,7 +42520,7 @@
         <v>46037</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42593,7 +42593,7 @@
         <v>46042</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>45546</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42744,7 +42744,7 @@
         <v>46045</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>45252</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>45601</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>45323</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43036,7 +43036,7 @@
         <v>45624</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43109,7 +43109,7 @@
         <v>46049</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43182,7 +43182,7 @@
         <v>46052</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43255,7 +43255,7 @@
         <v>46055</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43328,7 +43328,7 @@
         <v>45966</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43401,7 +43401,7 @@
         <v>46142</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43474,7 +43474,7 @@
         <v>46142</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43547,7 +43547,7 @@
         <v>46065</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43620,7 +43620,7 @@
         <v>46070</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43693,7 +43693,7 @@
         <v>46069</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43766,7 +43766,7 @@
         <v>46077</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43839,7 +43839,7 @@
         <v>46082</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43912,7 +43912,7 @@
         <v>46065</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43985,7 +43985,7 @@
         <v>46082</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44058,7 +44058,7 @@
         <v>45635</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>46087</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>45933</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>45959</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44350,7 +44350,7 @@
         <v>45959</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44423,7 +44423,7 @@
         <v>46162</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44496,7 +44496,7 @@
         <v>45482</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         <v>46097</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44642,7 +44642,7 @@
         <v>46162</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44715,7 +44715,7 @@
         <v>46164</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44788,7 +44788,7 @@
         <v>46164</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44861,7 +44861,7 @@
         <v>46164</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44934,7 +44934,7 @@
         <v>45923</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
         <v>46166</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45080,7 +45080,7 @@
         <v>44574</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45153,7 +45153,7 @@
         <v>46168</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>46172</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45299,7 +45299,7 @@
         <v>46170</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45372,7 +45372,7 @@
         <v>46007</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45445,7 +45445,7 @@
         <v>46178</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45518,7 +45518,7 @@
         <v>46182</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>46182</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45664,7 +45664,7 @@
         <v>46184</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45737,7 +45737,7 @@
         <v>46184</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45810,7 +45810,7 @@
         <v>46190</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45883,7 +45883,7 @@
         <v>46196</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45956,7 +45956,7 @@
         <v>46200</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46029,7 +46029,7 @@
         <v>46203</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46102,7 +46102,7 @@
         <v>46202</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
         <v>46202</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46253,7 +46253,7 @@
         <v>46202</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46331,7 +46331,7 @@
         <v>46203</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46404,7 +46404,7 @@
         <v>46211</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46477,7 +46477,7 @@
         <v>46212</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46550,7 +46550,7 @@
         <v>46212</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46623,7 +46623,7 @@
         <v>46217</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46696,7 +46696,7 @@
         <v>46263</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>46263</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46842,7 +46842,7 @@
         <v>46225</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46915,7 +46915,7 @@
         <v>46272</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>46272</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47061,7 +47061,7 @@
         <v>46204</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47134,7 +47134,7 @@
         <v>46282</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47207,7 +47207,7 @@
         <v>46282</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47280,7 +47280,7 @@
         <v>46281</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>46282</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47426,7 +47426,7 @@
         <v>46282</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47499,7 +47499,7 @@
         <v>46244</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47572,7 +47572,7 @@
         <v>46041</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47645,7 +47645,7 @@
         <v>46290</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47718,7 +47718,7 @@
         <v>46289</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>46282</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>46294</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47937,7 +47937,7 @@
         <v>46293</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48010,7 +48010,7 @@
         <v>46293</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>46248</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>46293</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>46293</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48302,7 +48302,7 @@
         <v>46293</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48375,7 +48375,7 @@
         <v>46296</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>46253</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48521,7 +48521,7 @@
         <v>46251</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48594,7 +48594,7 @@
         <v>46295</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>46271</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48740,7 +48740,7 @@
         <v>46271</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>46259</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48886,7 +48886,7 @@
         <v>46259</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48959,7 +48959,7 @@
         <v>46259</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49032,7 +49032,7 @@
         <v>46258</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49105,7 +49105,7 @@
         <v>46302</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49178,7 +49178,7 @@
         <v>46304</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49251,7 +49251,7 @@
         <v>46304</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49324,7 +49324,7 @@
         <v>46293</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49397,7 +49397,7 @@
         <v>46304</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         <v>46304</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49543,7 +49543,7 @@
         <v>46087</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49616,7 +49616,7 @@
         <v>46260</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49689,7 +49689,7 @@
         <v>44574</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>44608</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49840,7 +49840,7 @@
         <v>44636</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49913,7 +49913,7 @@
         <v>45259</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49986,7 +49986,7 @@
         <v>45352</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>45261</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>45370</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50205,7 +50205,7 @@
         <v>44489</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50283,7 +50283,7 @@
         <v>45356</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50356,7 +50356,7 @@
         <v>45330</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50429,7 +50429,7 @@
         <v>45349</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50502,7 +50502,7 @@
         <v>45352</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50575,7 +50575,7 @@
         <v>45435</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50648,7 +50648,7 @@
         <v>45370</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50721,7 +50721,7 @@
         <v>45580</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50794,7 +50794,7 @@
         <v>45370</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50867,7 +50867,7 @@
         <v>45335</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50940,7 +50940,7 @@
         <v>45534</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51013,7 +51013,7 @@
         <v>44967</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51086,7 +51086,7 @@
         <v>45352</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51159,7 +51159,7 @@
         <v>44489</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51237,7 +51237,7 @@
         <v>45744</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51310,7 +51310,7 @@
         <v>45744</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51383,7 +51383,7 @@
         <v>45750</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51456,7 +51456,7 @@
         <v>45756</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51529,7 +51529,7 @@
         <v>45715</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51602,7 +51602,7 @@
         <v>45910</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51675,7 +51675,7 @@
         <v>46020</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>46042</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51821,7 +51821,7 @@
         <v>46058</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51894,7 +51894,7 @@
         <v>46122</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51967,7 +51967,7 @@
         <v>46154</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>46154</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52113,7 +52113,7 @@
         <v>46154</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52186,7 +52186,7 @@
         <v>46154</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52259,7 +52259,7 @@
         <v>46160</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52332,7 +52332,7 @@
         <v>46206</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52405,7 +52405,7 @@
         <v>46253</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>

--- a/Översikt FALKENBERG.xlsx
+++ b/Översikt FALKENBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46247</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>46253</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>46255</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45560</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>46255</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45741</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>46282</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>44593</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>44592</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>44628</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>44516</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>45079</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>45356</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>45527</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>45680</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45335</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>45795</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>44616</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45600</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>45456</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44539</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>45356</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>44818</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44507</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>44517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>45561</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>45565</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>44972</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>45196</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>45667</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>45914</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>44946</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>44926</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>45355</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>45600</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>45239</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>45273</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>45068</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>45273</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>44902</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>46248</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>44705</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>44964</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>45352</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>45352</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>45349</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>45330</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>45945</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>46099</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44806</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>44607</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>44553</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>44539</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>44868</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>44867</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44680</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44600</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44868</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>44816</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>44613</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>44689</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>44616</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>44616</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>44617</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>44547</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44599</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>44711</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44879</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44544</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>44539</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>44719</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>44803</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>44600</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>44537</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>44628</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>44692</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>44692</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>44614</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>44600</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>44596</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>44866</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>44685</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>44539</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>44539</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>44638</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>44747</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         <v>44593</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>44813</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>44841</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>44545</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>44481</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>44543</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>44539</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>45232</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>44652</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>44893</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>45001</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>45681</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>45682</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>45682</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>45246</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>45673</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>45363</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>44539</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>44806</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>45321</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>45751</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>45627</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>45357</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>45119</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>45127</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>45705</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>45350</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>44985</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>44882</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>45548</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>45212</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>45212</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>45044</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>44631</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>45456</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>44957</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>45377</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>45174</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         <v>45426</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>44689</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>45229</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         <v>45195</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>44687</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>45702</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>45266</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>45664</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>45629</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>44538</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>45188</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>45400</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>44966</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>45350</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>45546</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44642</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>45280</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>45462</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>45435</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>44545</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>45686</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>45552</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>44903</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>45351</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>45597</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>45117</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>44846</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>45419</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>45324</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>45243</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>44999</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>44938</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>45120</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>45131</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>45142</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>45323</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>45037</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>44986</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>45681</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>45580</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>45147</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>44963</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>44963</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>45244</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         <v>44903</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>45533</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>45439</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>45239</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>45888</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
         <v>45219</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44908</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>44545</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15340,7 +15340,7 @@
         <v>45247</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>45782</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>45274</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>45425</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         <v>45582</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
         <v>45342</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>45474</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>45300</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>45300</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>45300</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>44946</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>45800</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>44525</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>45889</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>44543</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
         <v>44957</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>45019</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>45029</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>45441</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>45770</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>44986</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>45895</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>45895</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>45001</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>45644</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>45616</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>45667</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>45901</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>45127</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>45901</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>45670</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44827</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>45226</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>45138</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
         <v>44602</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17910,7 +17910,7 @@
         <v>45071</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         <v>45681</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>44897</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>45329</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18202,7 +18202,7 @@
         <v>45524</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>44916</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>45908</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>45300</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>44576</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>44622</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>45667</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>44900</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>44974</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45777</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         <v>44848</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>45566</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>45566</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>45566</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>45782</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
         <v>45105</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>45048</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19443,7 +19443,7 @@
         <v>45278</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>45914</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44584</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>45148</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>45328</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>45272</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>45554</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>45917</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>45349</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>44986</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45219</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20251,7 +20251,7 @@
         <v>45785</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>44622</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>45547</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20470,7 +20470,7 @@
         <v>45714</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>45350</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>45924</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>45741</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>45443</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>45923</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20908,7 +20908,7 @@
         <v>45552</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>45355</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21054,7 +21054,7 @@
         <v>45481</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>44938</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>45790</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>45562</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21346,7 +21346,7 @@
         <v>45923</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21419,7 +21419,7 @@
         <v>45923</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>45582</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         <v>45377</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>45926</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>45926</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>45552</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>45926</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>45926</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>45678</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22076,7 +22076,7 @@
         <v>45616</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>45401</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>45555</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>45686</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>44600</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>45714</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>45666</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>45588</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22665,7 +22665,7 @@
         <v>45748</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>45931</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>45931</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>45931</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>44974</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>45246</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>45667</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>44644</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>45575</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
         <v>45190</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>44554</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>45601</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>44656</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>44694</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>45435</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>45799</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>45799</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>45799</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>45618</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>45896</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>44610</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>45896</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>45055</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>45055</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24417,7 +24417,7 @@
         <v>45575</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24490,7 +24490,7 @@
         <v>45273</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24563,7 +24563,7 @@
         <v>45643</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45937</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>45741</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         <v>45810</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>45182</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24938,7 +24938,7 @@
         <v>45751</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>45940</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>45187</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25157,7 +25157,7 @@
         <v>45946</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>45946</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>45946</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>45266</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>45467</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25522,7 +25522,7 @@
         <v>45615</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25595,7 +25595,7 @@
         <v>45401</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>45712</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25746,7 +25746,7 @@
         <v>45581</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25819,7 +25819,7 @@
         <v>45630</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>45714</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>45950</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26043,7 +26043,7 @@
         <v>45435</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>45821</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26189,7 +26189,7 @@
         <v>44946</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26262,7 +26262,7 @@
         <v>45952</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26335,7 +26335,7 @@
         <v>45414</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>44811</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>45188</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26559,7 +26559,7 @@
         <v>45181</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26632,7 +26632,7 @@
         <v>45951</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>45667</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>45952</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26856,7 +26856,7 @@
         <v>45952</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>45202</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27002,7 +27002,7 @@
         <v>45953</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27075,7 +27075,7 @@
         <v>45953</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27148,7 +27148,7 @@
         <v>45954</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>45959</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27294,7 +27294,7 @@
         <v>45950</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
         <v>45960</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>45959</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
         <v>45959</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>45959</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>45960</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>45834</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>45058</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>45834</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27956,7 +27956,7 @@
         <v>45015</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>44664</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>45964</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>45834</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>45084</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>45680</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28399,7 +28399,7 @@
         <v>45838</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>45838</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>45679</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28623,7 +28623,7 @@
         <v>44964</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>45838</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28769,7 +28769,7 @@
         <v>45474</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28842,7 +28842,7 @@
         <v>45838</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28915,7 +28915,7 @@
         <v>45961</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>45838</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>45965</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29134,7 +29134,7 @@
         <v>45163</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29207,7 +29207,7 @@
         <v>45182</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>45188</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29353,7 +29353,7 @@
         <v>45965</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29426,7 +29426,7 @@
         <v>45965</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>44977</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>45965</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>45965</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>45965</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>45965</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>45965</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>45968</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>45131</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>45968</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>45035</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         <v>45971</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>45239</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>45971</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>45971</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>45582</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>45300</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30677,7 +30677,7 @@
         <v>45971</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>44984</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>45845</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>45595</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>45973</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>45848</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
         <v>45187</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>45174</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>45973</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>45152</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>44986</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>45174</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>45174</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>45328</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>45189</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>45750</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>45762</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>45343</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>44852</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>45975</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>45800</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>44524</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>44627</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>45777</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>45714</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>44515</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>44521</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>45736</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>45422</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>45422</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32897,7 +32897,7 @@
         <v>45422</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32975,7 +32975,7 @@
         <v>44818</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33053,7 +33053,7 @@
         <v>45068</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33126,7 +33126,7 @@
         <v>44866</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>45387</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>45434</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>45229</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>45273</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33491,7 +33491,7 @@
         <v>45079</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>45305</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33637,7 +33637,7 @@
         <v>45035</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>44693</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>44952</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>45817</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>45146</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34002,7 +34002,7 @@
         <v>45840</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>45337</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>44952</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34226,7 +34226,7 @@
         <v>45761</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>45280</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34372,7 +34372,7 @@
         <v>45337</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34445,7 +34445,7 @@
         <v>45068</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34518,7 +34518,7 @@
         <v>45074</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         <v>45270</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34664,7 +34664,7 @@
         <v>45249</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>44846</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>45013</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>44846</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>45260</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35029,7 +35029,7 @@
         <v>45248</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35107,7 +35107,7 @@
         <v>45249</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35180,7 +35180,7 @@
         <v>45271</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35253,7 +35253,7 @@
         <v>45751</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35326,7 +35326,7 @@
         <v>45434</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>45215</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35472,7 +35472,7 @@
         <v>44767</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>45226</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35618,7 +35618,7 @@
         <v>45013</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         <v>45754</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>44502</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>45826</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35910,7 +35910,7 @@
         <v>45249</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35983,7 +35983,7 @@
         <v>45250</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>45243</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>44943</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>44943</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>45184</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>45184</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>45184</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>45272</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>44827</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36650,7 +36650,7 @@
         <v>44958</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45091</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>45118</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>45252</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36947,7 +36947,7 @@
         <v>44785</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37020,7 +37020,7 @@
         <v>45282</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37093,7 +37093,7 @@
         <v>44831</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45357</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37239,7 +37239,7 @@
         <v>45091</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37312,7 +37312,7 @@
         <v>45205</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>45201</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37463,7 +37463,7 @@
         <v>45539</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37536,7 +37536,7 @@
         <v>45238</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>45691</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>44946</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>44740</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37828,7 +37828,7 @@
         <v>44740</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37901,7 +37901,7 @@
         <v>46106</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>45566</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>45044</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38120,7 +38120,7 @@
         <v>45245</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>46106</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38266,7 +38266,7 @@
         <v>44910</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>44910</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45978</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         <v>45989</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38558,7 +38558,7 @@
         <v>45068</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38631,7 +38631,7 @@
         <v>45735</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45618</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38777,7 +38777,7 @@
         <v>45618</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38850,7 +38850,7 @@
         <v>45326</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38923,7 +38923,7 @@
         <v>45628</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>46120</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>44946</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>44627</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>45999</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>46127</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39371,7 +39371,7 @@
         <v>44887</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>44692</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>45560</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>45211</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39663,7 +39663,7 @@
         <v>45175</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>46003</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39809,7 +39809,7 @@
         <v>44970</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39882,7 +39882,7 @@
         <v>46006</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>46004</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40028,7 +40028,7 @@
         <v>45770</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
         <v>45580</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>45345</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>45189</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>44946</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>44946</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40471,7 +40471,7 @@
         <v>45357</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40544,7 +40544,7 @@
         <v>44974</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>45566</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>44806</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40763,7 +40763,7 @@
         <v>44517</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45188</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40909,7 +40909,7 @@
         <v>45182</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40982,7 +40982,7 @@
         <v>45772</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41055,7 +41055,7 @@
         <v>45831</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41128,7 +41128,7 @@
         <v>45391</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41201,7 +41201,7 @@
         <v>45953</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>45381</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41347,7 +41347,7 @@
         <v>45384</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41420,7 +41420,7 @@
         <v>45390</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>45764</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>45856</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>45709</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41712,7 +41712,7 @@
         <v>45363</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41785,7 +41785,7 @@
         <v>45036</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41858,7 +41858,7 @@
         <v>45811</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41931,7 +41931,7 @@
         <v>45435</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42004,7 +42004,7 @@
         <v>44984</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>45435</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42150,7 +42150,7 @@
         <v>45076</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42223,7 +42223,7 @@
         <v>45842</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>45561</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>46035</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42442,7 +42442,7 @@
         <v>46037</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42520,7 +42520,7 @@
         <v>46037</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42593,7 +42593,7 @@
         <v>46042</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>45546</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42744,7 +42744,7 @@
         <v>46045</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>45252</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42890,7 +42890,7 @@
         <v>45601</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>45323</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43036,7 +43036,7 @@
         <v>45624</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43109,7 +43109,7 @@
         <v>46049</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43182,7 +43182,7 @@
         <v>46052</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43255,7 +43255,7 @@
         <v>46055</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43328,7 +43328,7 @@
         <v>45966</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43401,7 +43401,7 @@
         <v>46142</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43474,7 +43474,7 @@
         <v>46142</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43547,7 +43547,7 @@
         <v>46065</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43620,7 +43620,7 @@
         <v>46070</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43693,7 +43693,7 @@
         <v>46069</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43766,7 +43766,7 @@
         <v>46077</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43839,7 +43839,7 @@
         <v>46082</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43912,7 +43912,7 @@
         <v>46065</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43985,7 +43985,7 @@
         <v>46082</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44058,7 +44058,7 @@
         <v>45635</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>46087</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>45933</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>45959</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44350,7 +44350,7 @@
         <v>45959</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44423,7 +44423,7 @@
         <v>46162</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44496,7 +44496,7 @@
         <v>45482</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         <v>46097</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44642,7 +44642,7 @@
         <v>46162</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44715,7 +44715,7 @@
         <v>46164</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44788,7 +44788,7 @@
         <v>46164</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44861,7 +44861,7 @@
         <v>46164</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44934,7 +44934,7 @@
         <v>45923</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
         <v>46166</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45080,7 +45080,7 @@
         <v>44574</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45153,7 +45153,7 @@
         <v>46168</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>46172</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45299,7 +45299,7 @@
         <v>46170</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45372,7 +45372,7 @@
         <v>46007</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45445,7 +45445,7 @@
         <v>46178</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45518,7 +45518,7 @@
         <v>46182</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>46182</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45664,7 +45664,7 @@
         <v>46184</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45737,7 +45737,7 @@
         <v>46184</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45810,7 +45810,7 @@
         <v>46190</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45883,7 +45883,7 @@
         <v>46196</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45956,7 +45956,7 @@
         <v>46200</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46029,7 +46029,7 @@
         <v>46203</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46102,7 +46102,7 @@
         <v>46202</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46175,7 +46175,7 @@
         <v>46202</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46253,7 +46253,7 @@
         <v>46202</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46331,7 +46331,7 @@
         <v>46203</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46404,7 +46404,7 @@
         <v>46211</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46477,7 +46477,7 @@
         <v>46212</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46550,7 +46550,7 @@
         <v>46212</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46623,7 +46623,7 @@
         <v>46217</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46696,7 +46696,7 @@
         <v>46263</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>46263</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46842,7 +46842,7 @@
         <v>46225</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46915,7 +46915,7 @@
         <v>46272</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>46272</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47061,7 +47061,7 @@
         <v>46204</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47134,7 +47134,7 @@
         <v>46282</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47207,7 +47207,7 @@
         <v>46282</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47280,7 +47280,7 @@
         <v>46281</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>46282</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47426,7 +47426,7 @@
         <v>46282</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47499,7 +47499,7 @@
         <v>46244</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47572,7 +47572,7 @@
         <v>46041</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47645,7 +47645,7 @@
         <v>46290</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47718,7 +47718,7 @@
         <v>46289</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>46282</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>46294</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47937,7 +47937,7 @@
         <v>46293</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48010,7 +48010,7 @@
         <v>46293</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>46248</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>46293</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>46293</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48302,7 +48302,7 @@
         <v>46293</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48375,7 +48375,7 @@
         <v>46296</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>46253</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48521,7 +48521,7 @@
         <v>46251</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48594,7 +48594,7 @@
         <v>46295</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>46271</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48740,7 +48740,7 @@
         <v>46271</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>46259</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48886,7 +48886,7 @@
         <v>46259</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48959,7 +48959,7 @@
         <v>46259</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49032,7 +49032,7 @@
         <v>46258</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49105,7 +49105,7 @@
         <v>46302</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49178,7 +49178,7 @@
         <v>46304</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49251,7 +49251,7 @@
         <v>46304</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49324,7 +49324,7 @@
         <v>46293</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49397,7 +49397,7 @@
         <v>46304</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         <v>46304</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49543,7 +49543,7 @@
         <v>46087</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49616,7 +49616,7 @@
         <v>46260</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49689,7 +49689,7 @@
         <v>44574</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>44608</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49840,7 +49840,7 @@
         <v>44636</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49913,7 +49913,7 @@
         <v>45259</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49986,7 +49986,7 @@
         <v>45352</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>45261</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>45370</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50205,7 +50205,7 @@
         <v>44489</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50283,7 +50283,7 @@
         <v>45356</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50356,7 +50356,7 @@
         <v>45330</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50429,7 +50429,7 @@
         <v>45349</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50502,7 +50502,7 @@
         <v>45352</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50575,7 +50575,7 @@
         <v>45435</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50648,7 +50648,7 @@
         <v>45370</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50721,7 +50721,7 @@
         <v>45580</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50794,7 +50794,7 @@
         <v>45370</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50867,7 +50867,7 @@
         <v>45335</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50940,7 +50940,7 @@
         <v>45534</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51013,7 +51013,7 @@
         <v>44967</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51086,7 +51086,7 @@
         <v>45352</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51159,7 +51159,7 @@
         <v>44489</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51237,7 +51237,7 @@
         <v>45744</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51310,7 +51310,7 @@
         <v>45744</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51383,7 +51383,7 @@
         <v>45750</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51456,7 +51456,7 @@
         <v>45756</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51529,7 +51529,7 @@
         <v>45715</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51602,7 +51602,7 @@
         <v>45910</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51675,7 +51675,7 @@
         <v>46020</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>46042</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51821,7 +51821,7 @@
         <v>46058</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51894,7 +51894,7 @@
         <v>46122</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51967,7 +51967,7 @@
         <v>46154</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>46154</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52113,7 +52113,7 @@
         <v>46154</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52186,7 +52186,7 @@
         <v>46154</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52259,7 +52259,7 @@
         <v>46160</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52332,7 +52332,7 @@
         <v>46206</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52405,7 +52405,7 @@
         <v>46253</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>

--- a/Översikt FALKENBERG.xlsx
+++ b/Översikt FALKENBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46247</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>46253</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>46255</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45560</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>46255</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45741</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>46282</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>44592</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>44593</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>44516</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>44628</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>45079</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>45356</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>45527</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>45680</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45795</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>45335</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>44616</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>45600</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>45456</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>45356</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>44818</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44507</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>44517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>45196</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>45600</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>45355</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>44946</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>45667</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>45914</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>44926</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>45561</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>44902</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>45565</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>45239</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>44972</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>46248</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>45273</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>45068</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>45273</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>44964</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45352</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>45352</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45349</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>44705</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>45330</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>45945</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>46099</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44806</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>44607</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>44553</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>44539</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>44868</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>44867</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44680</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44868</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44600</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>44816</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>44613</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>44689</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>44616</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>44616</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>44617</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>44547</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44599</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>44711</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44879</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44544</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>44600</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>44692</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>44692</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>44600</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>44539</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>44539</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>44747</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>44813</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>44841</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>44545</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>44719</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>44866</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>44593</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>44803</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>44614</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>44685</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>44596</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>44638</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>44539</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>44537</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>44628</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>44543</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>44539</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>44539</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>45321</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>44958</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>45425</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>44576</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>45363</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>44985</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>45552</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>45546</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>45735</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>45205</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>44946</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>45148</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>44848</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>45736</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>45419</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>45751</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>45147</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>45044</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>44893</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>44600</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>45714</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>44903</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>44525</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>44999</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>44986</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>45714</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>45772</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45300</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>45152</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>45001</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>44946</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>44946</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>45201</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>44545</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>45019</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>45343</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>45441</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>45435</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>45127</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
         <v>45435</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>44882</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>45189</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>44986</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>45091</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         <v>45595</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>44974</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>45324</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>44984</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>45548</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>45188</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>45188</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>44689</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>45682</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>45682</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>44974</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>45462</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>45552</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13457,7 +13457,7 @@
         <v>45252</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>45226</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>45481</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>45435</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>45232</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>45182</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13895,7 +13895,7 @@
         <v>44903</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>45015</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14041,7 +14041,7 @@
         <v>45219</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>44887</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14187,7 +14187,7 @@
         <v>44811</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>45182</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>45272</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14406,7 +14406,7 @@
         <v>45350</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>45044</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>45243</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>45555</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>45533</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>45575</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>45581</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         <v>44910</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>45681</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>45329</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>45800</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>45770</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15287,7 +15287,7 @@
         <v>45673</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
         <v>45842</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>45764</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>45782</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>45582</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>44642</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15725,7 +15725,7 @@
         <v>45889</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>44687</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>45888</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>45770</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>45895</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>45895</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>44908</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>45524</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>44644</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>45552</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>45390</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>45811</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>45901</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>45901</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>45280</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>45187</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>45566</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>45246</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44631</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>45670</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>44584</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45163</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>45908</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>45350</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>46142</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>45195</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>46142</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17696,7 +17696,7 @@
         <v>45914</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>45917</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>44946</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>45546</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45923</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45923</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>45923</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>45691</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>45924</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>45681</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>45926</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>45926</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>45926</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         <v>45926</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>45091</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>44977</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>45931</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>45931</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>45931</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>45896</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>45667</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>45896</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>45401</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>45937</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19468,7 +19468,7 @@
         <v>45940</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>45202</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>45946</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>45751</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>45946</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>45959</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>44970</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19979,7 +19979,7 @@
         <v>45946</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         <v>44963</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20125,7 +20125,7 @@
         <v>44963</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>45959</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20271,7 +20271,7 @@
         <v>45951</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>45950</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>45635</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>45952</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>45952</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>45953</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>45953</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20787,7 +20787,7 @@
         <v>45952</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>45328</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>45954</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21011,7 +21011,7 @@
         <v>45933</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>45959</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>45959</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21230,7 +21230,7 @@
         <v>45959</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>45959</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>45950</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>45960</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>45961</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>45482</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>45618</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>45960</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>45965</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>45964</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>45965</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>45965</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>45965</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22189,7 +22189,7 @@
         <v>45965</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22262,7 +22262,7 @@
         <v>45965</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>45965</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22408,7 +22408,7 @@
         <v>45667</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>44986</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>45968</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22627,7 +22627,7 @@
         <v>45971</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>45971</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>45971</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>45377</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>45580</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>45968</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         <v>46162</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>45971</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23211,7 +23211,7 @@
         <v>45973</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>45973</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45975</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23440,7 +23440,7 @@
         <v>45539</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>44957</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>44543</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         <v>45084</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23732,7 +23732,7 @@
         <v>46162</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>45547</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23878,7 +23878,7 @@
         <v>46164</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>45414</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>45978</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>45037</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>46164</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>44622</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>44622</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>46166</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>46164</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>45350</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24613,7 +24613,7 @@
         <v>45989</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>44574</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45566</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>44554</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>45616</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>45435</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>45999</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>45644</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>45618</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>45923</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25343,7 +25343,7 @@
         <v>46168</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>45300</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>45456</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25562,7 +25562,7 @@
         <v>45188</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>46170</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>45667</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25781,7 +25781,7 @@
         <v>45705</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>46003</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>44897</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45266</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>46004</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>46006</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>45323</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>44610</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>45953</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>44740</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>46172</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>45628</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>45048</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>45566</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>45566</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>45566</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>45036</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27027,7 +27027,7 @@
         <v>44827</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>46035</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>46037</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>46037</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>46007</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27397,7 +27397,7 @@
         <v>44831</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27470,7 +27470,7 @@
         <v>45138</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>45326</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>46042</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27689,7 +27689,7 @@
         <v>45681</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27762,7 +27762,7 @@
         <v>45751</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>46178</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>44538</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>44740</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45667</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>45189</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>44652</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>45686</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>46045</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>46182</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>46049</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28570,7 +28570,7 @@
         <v>45741</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>44524</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>46182</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         <v>45678</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>46055</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>46052</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29008,7 +29008,7 @@
         <v>44900</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>46184</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>45601</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29227,7 +29227,7 @@
         <v>45966</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>44986</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29373,7 +29373,7 @@
         <v>45714</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29446,7 +29446,7 @@
         <v>45391</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29519,7 +29519,7 @@
         <v>46065</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29592,7 +29592,7 @@
         <v>46184</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         <v>45300</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>46069</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29811,7 +29811,7 @@
         <v>46070</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>45068</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>46065</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>45188</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>45349</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30176,7 +30176,7 @@
         <v>46077</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>45174</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>45624</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>46190</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>46082</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>45401</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>45055</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30692,7 +30692,7 @@
         <v>45055</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>46082</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30838,7 +30838,7 @@
         <v>44656</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>44664</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30984,7 +30984,7 @@
         <v>46087</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31057,7 +31057,7 @@
         <v>45274</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31130,7 +31130,7 @@
         <v>44846</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31203,7 +31203,7 @@
         <v>46097</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>45643</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31354,7 +31354,7 @@
         <v>45345</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31427,7 +31427,7 @@
         <v>45119</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>46106</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>45266</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31646,7 +31646,7 @@
         <v>46106</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31719,7 +31719,7 @@
         <v>46196</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31792,7 +31792,7 @@
         <v>44916</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>45474</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31938,7 +31938,7 @@
         <v>46120</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32016,7 +32016,7 @@
         <v>46202</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32089,7 +32089,7 @@
         <v>46202</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>44946</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>46202</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>45058</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32391,7 +32391,7 @@
         <v>44545</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32464,7 +32464,7 @@
         <v>46200</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32537,7 +32537,7 @@
         <v>46127</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32610,7 +32610,7 @@
         <v>45384</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32683,7 +32683,7 @@
         <v>44938</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32756,7 +32756,7 @@
         <v>46203</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32829,7 +32829,7 @@
         <v>45187</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32902,7 +32902,7 @@
         <v>45131</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32975,7 +32975,7 @@
         <v>45105</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33048,7 +33048,7 @@
         <v>44806</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33121,7 +33121,7 @@
         <v>45211</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33194,7 +33194,7 @@
         <v>46203</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>45561</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33340,7 +33340,7 @@
         <v>45831</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         <v>45554</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33486,7 +33486,7 @@
         <v>45377</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33559,7 +33559,7 @@
         <v>45709</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>45400</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33705,7 +33705,7 @@
         <v>45856</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>45239</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>45219</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>45762</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>45244</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>44692</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34143,7 +34143,7 @@
         <v>44806</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>45212</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>45212</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>45426</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>45174</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34508,7 +34508,7 @@
         <v>46212</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>46212</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34654,7 +34654,7 @@
         <v>46211</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>45351</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34800,7 +34800,7 @@
         <v>45273</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34873,7 +34873,7 @@
         <v>45580</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34946,7 +34946,7 @@
         <v>44602</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>46217</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>45575</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35165,7 +35165,7 @@
         <v>45627</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>45474</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>45181</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>46225</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>45118</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>45247</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35603,7 +35603,7 @@
         <v>45601</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35676,7 +35676,7 @@
         <v>45300</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35749,7 +35749,7 @@
         <v>45300</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>46272</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35895,7 +35895,7 @@
         <v>46272</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35968,7 +35968,7 @@
         <v>45245</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36041,7 +36041,7 @@
         <v>44785</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36114,7 +36114,7 @@
         <v>45182</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36187,7 +36187,7 @@
         <v>45702</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36260,7 +36260,7 @@
         <v>45252</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>45629</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>45239</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36479,7 +36479,7 @@
         <v>45272</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>45029</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>45680</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36698,7 +36698,7 @@
         <v>46281</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36771,7 +36771,7 @@
         <v>45190</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36844,7 +36844,7 @@
         <v>45363</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>44966</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>46282</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>45238</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>45597</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>46282</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37287,7 +37287,7 @@
         <v>45560</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>46282</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>46282</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37506,7 +37506,7 @@
         <v>45357</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37579,7 +37579,7 @@
         <v>45323</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37652,7 +37652,7 @@
         <v>46204</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37725,7 +37725,7 @@
         <v>45381</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>45127</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>45229</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37949,7 +37949,7 @@
         <v>45282</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38022,7 +38022,7 @@
         <v>45142</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38095,7 +38095,7 @@
         <v>45035</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38168,7 +38168,7 @@
         <v>44938</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>46041</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38314,7 +38314,7 @@
         <v>45120</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38387,7 +38387,7 @@
         <v>45664</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38460,7 +38460,7 @@
         <v>44627</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38533,7 +38533,7 @@
         <v>45001</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38606,7 +38606,7 @@
         <v>44910</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38679,7 +38679,7 @@
         <v>46244</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38752,7 +38752,7 @@
         <v>44957</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38825,7 +38825,7 @@
         <v>45246</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38898,7 +38898,7 @@
         <v>46282</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38971,7 +38971,7 @@
         <v>44827</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>45435</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>45342</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39195,7 +39195,7 @@
         <v>45714</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39268,7 +39268,7 @@
         <v>46293</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39341,7 +39341,7 @@
         <v>46293</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39414,7 +39414,7 @@
         <v>46290</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>46293</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39560,7 +39560,7 @@
         <v>45618</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39633,7 +39633,7 @@
         <v>44694</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>46293</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>45588</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45076</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>44517</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39998,7 +39998,7 @@
         <v>46248</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>44852</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>46289</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>45131</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40290,7 +40290,7 @@
         <v>45357</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40363,7 +40363,7 @@
         <v>44627</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>45357</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>45226</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40582,7 +40582,7 @@
         <v>44974</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40655,7 +40655,7 @@
         <v>46295</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40728,7 +40728,7 @@
         <v>44964</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40801,7 +40801,7 @@
         <v>45355</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40874,7 +40874,7 @@
         <v>46294</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>45117</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>46251</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41093,7 +41093,7 @@
         <v>44946</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41166,7 +41166,7 @@
         <v>45439</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>45175</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41312,7 +41312,7 @@
         <v>45174</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         <v>45174</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>45328</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>46296</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41609,7 +41609,7 @@
         <v>46253</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>45035</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41755,7 +41755,7 @@
         <v>45582</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41828,7 +41828,7 @@
         <v>45071</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>45777</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41974,7 +41974,7 @@
         <v>46258</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>45782</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42120,7 +42120,7 @@
         <v>46271</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42193,7 +42193,7 @@
         <v>46271</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42266,7 +42266,7 @@
         <v>45278</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42339,7 +42339,7 @@
         <v>45785</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42412,7 +42412,7 @@
         <v>45741</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         <v>45562</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>45443</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>46259</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42704,7 +42704,7 @@
         <v>45582</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42777,7 +42777,7 @@
         <v>46259</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>46302</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45616</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>46260</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>46259</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>45790</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>46307</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>45748</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>45686</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43434,7 +43434,7 @@
         <v>46263</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>46304</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43580,7 +43580,7 @@
         <v>46304</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>46263</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43726,7 +43726,7 @@
         <v>45666</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>45799</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43872,7 +43872,7 @@
         <v>46304</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43945,7 +43945,7 @@
         <v>46304</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44018,7 +44018,7 @@
         <v>46307</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>46307</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44164,7 +44164,7 @@
         <v>46293</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44237,7 +44237,7 @@
         <v>46293</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44310,7 +44310,7 @@
         <v>45799</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44383,7 +44383,7 @@
         <v>45799</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>45810</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44529,7 +44529,7 @@
         <v>46310</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44602,7 +44602,7 @@
         <v>46087</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44675,7 +44675,7 @@
         <v>45467</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44748,7 +44748,7 @@
         <v>45712</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>45630</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>45615</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44967,7 +44967,7 @@
         <v>45821</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>46310</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45113,7 +45113,7 @@
         <v>45834</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45186,7 +45186,7 @@
         <v>45834</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45259,7 +45259,7 @@
         <v>45834</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45838</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45405,7 +45405,7 @@
         <v>45838</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45478,7 +45478,7 @@
         <v>45838</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45551,7 +45551,7 @@
         <v>45838</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45838</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45697,7 +45697,7 @@
         <v>45845</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45770,7 +45770,7 @@
         <v>44984</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>45848</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45916,7 +45916,7 @@
         <v>45750</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45777</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46062,7 +46062,7 @@
         <v>45800</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46135,7 +46135,7 @@
         <v>45184</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>45184</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46281,7 +46281,7 @@
         <v>45337</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45249</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>44846</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>44846</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>45840</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46651,7 +46651,7 @@
         <v>45826</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46724,7 +46724,7 @@
         <v>45422</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         <v>45184</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>45013</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>45273</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>45280</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47094,7 +47094,7 @@
         <v>44767</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47167,7 +47167,7 @@
         <v>45079</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47240,7 +47240,7 @@
         <v>45817</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>44693</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45434</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47459,7 +47459,7 @@
         <v>45013</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47532,7 +47532,7 @@
         <v>45074</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>44943</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47683,7 +47683,7 @@
         <v>44943</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47761,7 +47761,7 @@
         <v>44818</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>44502</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>45215</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>44515</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>45337</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48131,7 +48131,7 @@
         <v>45387</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48204,7 +48204,7 @@
         <v>45761</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>45754</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>45068</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48423,7 +48423,7 @@
         <v>44866</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>45260</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>45422</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48647,7 +48647,7 @@
         <v>45271</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48720,7 +48720,7 @@
         <v>44521</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48793,7 +48793,7 @@
         <v>45243</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>45250</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>45248</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49017,7 +49017,7 @@
         <v>45249</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>45270</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49163,7 +49163,7 @@
         <v>44952</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45422</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49314,7 +49314,7 @@
         <v>45229</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>45249</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>44952</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49533,7 +49533,7 @@
         <v>45434</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49606,7 +49606,7 @@
         <v>45146</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49679,7 +49679,7 @@
         <v>45068</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49752,7 +49752,7 @@
         <v>45305</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49825,7 +49825,7 @@
         <v>44574</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49903,7 +49903,7 @@
         <v>45259</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49976,7 +49976,7 @@
         <v>45352</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50049,7 +50049,7 @@
         <v>44608</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50122,7 +50122,7 @@
         <v>45261</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50195,7 +50195,7 @@
         <v>44636</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50268,7 +50268,7 @@
         <v>45370</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50341,7 +50341,7 @@
         <v>44489</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50419,7 +50419,7 @@
         <v>45356</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50492,7 +50492,7 @@
         <v>45330</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50565,7 +50565,7 @@
         <v>45349</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50638,7 +50638,7 @@
         <v>45352</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50711,7 +50711,7 @@
         <v>45435</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50784,7 +50784,7 @@
         <v>45370</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50857,7 +50857,7 @@
         <v>45580</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45370</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51003,7 +51003,7 @@
         <v>45335</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>45534</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51149,7 +51149,7 @@
         <v>44967</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51222,7 +51222,7 @@
         <v>45352</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51295,7 +51295,7 @@
         <v>44489</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51373,7 +51373,7 @@
         <v>45744</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51446,7 +51446,7 @@
         <v>45744</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51519,7 +51519,7 @@
         <v>45750</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51592,7 +51592,7 @@
         <v>45756</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51665,7 +51665,7 @@
         <v>45715</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51738,7 +51738,7 @@
         <v>45910</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51811,7 +51811,7 @@
         <v>46020</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51884,7 +51884,7 @@
         <v>46042</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51957,7 +51957,7 @@
         <v>46058</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52030,7 +52030,7 @@
         <v>46122</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52103,7 +52103,7 @@
         <v>46154</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52176,7 +52176,7 @@
         <v>46154</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52249,7 +52249,7 @@
         <v>46154</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52322,7 +52322,7 @@
         <v>46154</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52395,7 +52395,7 @@
         <v>46160</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52468,7 +52468,7 @@
         <v>46206</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52541,7 +52541,7 @@
         <v>46253</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52619,7 +52619,7 @@
         <v>46308</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>

--- a/Översikt FALKENBERG.xlsx
+++ b/Översikt FALKENBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46247</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>46253</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>46255</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45560</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>46255</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45741</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>46282</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>44592</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>44593</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>44516</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>44628</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>45079</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>45356</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>45527</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>45680</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45795</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>45335</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>44539</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>44616</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>45600</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>45456</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>45356</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>44818</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44507</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>44517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>45196</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>45600</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>45355</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>44946</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>45667</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>45914</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>44926</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>45561</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>44902</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>45565</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>45239</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>44972</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>46248</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>45273</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>45068</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>45273</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>44964</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45352</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>45352</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45349</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>44705</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>45330</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>45945</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>46099</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44806</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>44607</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>44553</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>44539</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>44868</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>44867</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44680</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44868</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44600</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>44816</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>44613</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>44689</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>44616</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>44616</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>44617</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>44547</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44599</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>44711</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44879</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44544</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>44600</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>44692</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>44692</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>44600</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>44539</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>44539</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>44747</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>44813</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>44841</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>44545</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>44719</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>44866</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>44593</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>44803</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>44614</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>44685</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>44596</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>44638</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>44539</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>44537</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>44628</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>44543</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>44539</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>44539</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>45321</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>44958</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>45425</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>44576</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>45363</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>44985</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>45552</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>45546</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>45735</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>45205</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>44946</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>45148</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>44848</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>45736</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>45419</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>45751</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>45147</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>45044</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>44893</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>44600</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>45714</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>44903</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>44525</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>44999</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>44986</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>45714</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>45772</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45300</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>45152</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>45001</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>44946</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>44946</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>45201</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>44545</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>45019</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>45343</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>45441</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>45435</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>45127</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
         <v>45435</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>44882</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>45189</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>44986</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>45091</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         <v>45595</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>44974</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>45324</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>44984</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>45548</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>45188</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>45188</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>44689</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>45682</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>45682</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>44974</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>45462</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>45552</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13457,7 +13457,7 @@
         <v>45252</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>45226</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>45481</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>45435</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>45232</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>45182</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13895,7 +13895,7 @@
         <v>44903</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>45015</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14041,7 +14041,7 @@
         <v>45219</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>44887</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14187,7 +14187,7 @@
         <v>44811</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>45182</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>45272</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14406,7 +14406,7 @@
         <v>45350</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>45044</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>45243</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>45555</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>45533</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>45575</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>45581</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         <v>44910</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>45681</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>45329</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>45800</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>45770</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15287,7 +15287,7 @@
         <v>45673</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
         <v>45842</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>45764</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>45782</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>45582</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>44642</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15725,7 +15725,7 @@
         <v>45889</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>44687</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>45888</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>45770</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>45895</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>45895</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>44908</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>45524</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>44644</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>45552</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>45390</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>45811</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>45901</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>45901</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>45280</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>45187</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>45566</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>45246</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44631</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>45670</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>44584</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45163</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>45908</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>45350</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>46142</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>45195</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>46142</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17696,7 +17696,7 @@
         <v>45914</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>45917</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>44946</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>45546</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45923</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45923</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>45923</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>45691</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>45924</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>45681</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>45926</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>45926</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>45926</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         <v>45926</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>45091</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>44977</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>45931</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>45931</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>45931</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>45896</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>45667</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>45896</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>45401</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>45937</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19468,7 +19468,7 @@
         <v>45940</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>45202</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>45946</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>45751</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>45946</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>45959</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>44970</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19979,7 +19979,7 @@
         <v>45946</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         <v>44963</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20125,7 +20125,7 @@
         <v>44963</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>45959</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20271,7 +20271,7 @@
         <v>45951</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>45950</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>45635</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>45952</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>45952</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>45953</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>45953</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20787,7 +20787,7 @@
         <v>45952</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>45328</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>45954</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21011,7 +21011,7 @@
         <v>45933</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>45959</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>45959</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21230,7 +21230,7 @@
         <v>45959</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>45959</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>45950</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>45960</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>45961</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>45482</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>45618</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>45960</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>45965</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>45964</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>45965</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>45965</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>45965</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22189,7 +22189,7 @@
         <v>45965</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22262,7 +22262,7 @@
         <v>45965</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>45965</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22408,7 +22408,7 @@
         <v>45667</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>44986</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>45968</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22627,7 +22627,7 @@
         <v>45971</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>45971</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>45971</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>45377</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>45580</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>45968</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         <v>46162</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>45971</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23211,7 +23211,7 @@
         <v>45973</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>45973</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45975</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23440,7 +23440,7 @@
         <v>45539</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>44957</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>44543</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         <v>45084</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23732,7 +23732,7 @@
         <v>46162</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>45547</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23878,7 +23878,7 @@
         <v>46164</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>45414</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>45978</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>45037</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>46164</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>44622</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>44622</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>46166</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>46164</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>45350</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24613,7 +24613,7 @@
         <v>45989</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>44574</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45566</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>44554</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>45616</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>45435</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>45999</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>45644</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>45618</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>45923</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25343,7 +25343,7 @@
         <v>46168</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>45300</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>45456</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25562,7 +25562,7 @@
         <v>45188</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>46170</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>45667</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25781,7 +25781,7 @@
         <v>45705</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>46003</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>44897</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45266</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>46004</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>46006</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>45323</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>44610</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>45953</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>44740</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>46172</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>45628</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>45048</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>45566</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>45566</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>45566</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>45036</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27027,7 +27027,7 @@
         <v>44827</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>46035</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>46037</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>46037</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>46007</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27397,7 +27397,7 @@
         <v>44831</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27470,7 +27470,7 @@
         <v>45138</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>45326</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>46042</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27689,7 +27689,7 @@
         <v>45681</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27762,7 +27762,7 @@
         <v>45751</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>46178</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>44538</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>44740</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45667</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>45189</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>44652</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>45686</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>46045</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>46182</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>46049</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28570,7 +28570,7 @@
         <v>45741</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>44524</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>46182</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         <v>45678</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>46055</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>46052</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29008,7 +29008,7 @@
         <v>44900</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>46184</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>45601</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29227,7 +29227,7 @@
         <v>45966</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>44986</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29373,7 +29373,7 @@
         <v>45714</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29446,7 +29446,7 @@
         <v>45391</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29519,7 +29519,7 @@
         <v>46065</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29592,7 +29592,7 @@
         <v>46184</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         <v>45300</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>46069</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29811,7 +29811,7 @@
         <v>46070</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>45068</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>46065</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>45188</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>45349</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30176,7 +30176,7 @@
         <v>46077</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>45174</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>45624</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>46190</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>46082</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>45401</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>45055</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30692,7 +30692,7 @@
         <v>45055</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>46082</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30838,7 +30838,7 @@
         <v>44656</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>44664</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30984,7 +30984,7 @@
         <v>46087</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31057,7 +31057,7 @@
         <v>45274</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31130,7 +31130,7 @@
         <v>44846</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31203,7 +31203,7 @@
         <v>46097</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>45643</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31354,7 +31354,7 @@
         <v>45345</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31427,7 +31427,7 @@
         <v>45119</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>46106</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>45266</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31646,7 +31646,7 @@
         <v>46106</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31719,7 +31719,7 @@
         <v>46196</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31792,7 +31792,7 @@
         <v>44916</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>45474</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31938,7 +31938,7 @@
         <v>46120</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32016,7 +32016,7 @@
         <v>46202</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32089,7 +32089,7 @@
         <v>46202</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>44946</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>46202</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>45058</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32391,7 +32391,7 @@
         <v>44545</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32464,7 +32464,7 @@
         <v>46200</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32537,7 +32537,7 @@
         <v>46127</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32610,7 +32610,7 @@
         <v>45384</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32683,7 +32683,7 @@
         <v>44938</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32756,7 +32756,7 @@
         <v>46203</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32829,7 +32829,7 @@
         <v>45187</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32902,7 +32902,7 @@
         <v>45131</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32975,7 +32975,7 @@
         <v>45105</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33048,7 +33048,7 @@
         <v>44806</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33121,7 +33121,7 @@
         <v>45211</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33194,7 +33194,7 @@
         <v>46203</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>45561</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33340,7 +33340,7 @@
         <v>45831</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         <v>45554</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33486,7 +33486,7 @@
         <v>45377</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33559,7 +33559,7 @@
         <v>45709</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>45400</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33705,7 +33705,7 @@
         <v>45856</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>45239</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33851,7 +33851,7 @@
         <v>45219</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>45762</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>45244</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>44692</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34143,7 +34143,7 @@
         <v>44806</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>45212</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>45212</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>45426</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>45174</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34508,7 +34508,7 @@
         <v>46212</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>46212</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34654,7 +34654,7 @@
         <v>46211</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>45351</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34800,7 +34800,7 @@
         <v>45273</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34873,7 +34873,7 @@
         <v>45580</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34946,7 +34946,7 @@
         <v>44602</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>46217</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>45575</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35165,7 +35165,7 @@
         <v>45627</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>45474</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>45181</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>46225</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>45118</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>45247</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35603,7 +35603,7 @@
         <v>45601</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35676,7 +35676,7 @@
         <v>45300</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35749,7 +35749,7 @@
         <v>45300</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>46272</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35895,7 +35895,7 @@
         <v>46272</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35968,7 +35968,7 @@
         <v>45245</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36041,7 +36041,7 @@
         <v>44785</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36114,7 +36114,7 @@
         <v>45182</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36187,7 +36187,7 @@
         <v>45702</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36260,7 +36260,7 @@
         <v>45252</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>45629</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>45239</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36479,7 +36479,7 @@
         <v>45272</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>45029</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>45680</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36698,7 +36698,7 @@
         <v>46281</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36771,7 +36771,7 @@
         <v>45190</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36844,7 +36844,7 @@
         <v>45363</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>44966</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>46282</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>45238</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>45597</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>46282</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37287,7 +37287,7 @@
         <v>45560</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>46282</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>46282</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37506,7 +37506,7 @@
         <v>45357</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37579,7 +37579,7 @@
         <v>45323</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37652,7 +37652,7 @@
         <v>46204</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37725,7 +37725,7 @@
         <v>45381</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>45127</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>45229</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37949,7 +37949,7 @@
         <v>45282</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38022,7 +38022,7 @@
         <v>45142</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38095,7 +38095,7 @@
         <v>45035</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38168,7 +38168,7 @@
         <v>44938</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>46041</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38314,7 +38314,7 @@
         <v>45120</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38387,7 +38387,7 @@
         <v>45664</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38460,7 +38460,7 @@
         <v>44627</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38533,7 +38533,7 @@
         <v>45001</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38606,7 +38606,7 @@
         <v>44910</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38679,7 +38679,7 @@
         <v>46244</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38752,7 +38752,7 @@
         <v>44957</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38825,7 +38825,7 @@
         <v>45246</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38898,7 +38898,7 @@
         <v>46282</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38971,7 +38971,7 @@
         <v>44827</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>45435</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>45342</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39195,7 +39195,7 @@
         <v>45714</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39268,7 +39268,7 @@
         <v>46293</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39341,7 +39341,7 @@
         <v>46293</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39414,7 +39414,7 @@
         <v>46290</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>46293</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39560,7 +39560,7 @@
         <v>45618</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39633,7 +39633,7 @@
         <v>44694</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>46293</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>45588</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45076</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>44517</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39998,7 +39998,7 @@
         <v>46248</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>44852</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40144,7 +40144,7 @@
         <v>46289</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>45131</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40290,7 +40290,7 @@
         <v>45357</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40363,7 +40363,7 @@
         <v>44627</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>45357</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>45226</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40582,7 +40582,7 @@
         <v>44974</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40655,7 +40655,7 @@
         <v>46295</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40728,7 +40728,7 @@
         <v>44964</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40801,7 +40801,7 @@
         <v>45355</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40874,7 +40874,7 @@
         <v>46294</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>45117</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>46251</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41093,7 +41093,7 @@
         <v>44946</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41166,7 +41166,7 @@
         <v>45439</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>45175</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41312,7 +41312,7 @@
         <v>45174</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         <v>45174</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>45328</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>46296</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41609,7 +41609,7 @@
         <v>46253</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>45035</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41755,7 +41755,7 @@
         <v>45582</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41828,7 +41828,7 @@
         <v>45071</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>45777</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41974,7 +41974,7 @@
         <v>46258</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>45782</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42120,7 +42120,7 @@
         <v>46271</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42193,7 +42193,7 @@
         <v>46271</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42266,7 +42266,7 @@
         <v>45278</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42339,7 +42339,7 @@
         <v>45785</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42412,7 +42412,7 @@
         <v>45741</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         <v>45562</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>45443</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>46259</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42704,7 +42704,7 @@
         <v>45582</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42777,7 +42777,7 @@
         <v>46259</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>46302</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45616</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>46260</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>46259</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>45790</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>46307</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>45748</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>45686</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43434,7 +43434,7 @@
         <v>46263</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>46304</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43580,7 +43580,7 @@
         <v>46304</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>46263</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43726,7 +43726,7 @@
         <v>45666</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>45799</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43872,7 +43872,7 @@
         <v>46304</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43945,7 +43945,7 @@
         <v>46304</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44018,7 +44018,7 @@
         <v>46307</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>46307</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44164,7 +44164,7 @@
         <v>46293</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44237,7 +44237,7 @@
         <v>46293</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44310,7 +44310,7 @@
         <v>45799</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44383,7 +44383,7 @@
         <v>45799</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>45810</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44529,7 +44529,7 @@
         <v>46310</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44602,7 +44602,7 @@
         <v>46087</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44675,7 +44675,7 @@
         <v>45467</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44748,7 +44748,7 @@
         <v>45712</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44821,7 +44821,7 @@
         <v>45630</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>45615</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44967,7 +44967,7 @@
         <v>45821</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>46310</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45113,7 +45113,7 @@
         <v>45834</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45186,7 +45186,7 @@
         <v>45834</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45259,7 +45259,7 @@
         <v>45834</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45838</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45405,7 +45405,7 @@
         <v>45838</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45478,7 +45478,7 @@
         <v>45838</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45551,7 +45551,7 @@
         <v>45838</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45838</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45697,7 +45697,7 @@
         <v>45845</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45770,7 +45770,7 @@
         <v>44984</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>45848</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45916,7 +45916,7 @@
         <v>45750</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45777</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46062,7 +46062,7 @@
         <v>45800</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46135,7 +46135,7 @@
         <v>45184</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>45184</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46281,7 +46281,7 @@
         <v>45337</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45249</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>44846</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>44846</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>45840</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46651,7 +46651,7 @@
         <v>45826</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46724,7 +46724,7 @@
         <v>45422</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         <v>45184</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>45013</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>45273</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>45280</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47094,7 +47094,7 @@
         <v>44767</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47167,7 +47167,7 @@
         <v>45079</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47240,7 +47240,7 @@
         <v>45817</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>44693</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45434</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47459,7 +47459,7 @@
         <v>45013</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47532,7 +47532,7 @@
         <v>45074</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>44943</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47683,7 +47683,7 @@
         <v>44943</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47761,7 +47761,7 @@
         <v>44818</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>44502</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>45215</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>44515</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>45337</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48131,7 +48131,7 @@
         <v>45387</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48204,7 +48204,7 @@
         <v>45761</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>45754</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>45068</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48423,7 +48423,7 @@
         <v>44866</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>45260</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>45422</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48647,7 +48647,7 @@
         <v>45271</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48720,7 +48720,7 @@
         <v>44521</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48793,7 +48793,7 @@
         <v>45243</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>45250</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>45248</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49017,7 +49017,7 @@
         <v>45249</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>45270</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49163,7 +49163,7 @@
         <v>44952</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45422</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49314,7 +49314,7 @@
         <v>45229</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>45249</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>44952</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49533,7 +49533,7 @@
         <v>45434</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49606,7 +49606,7 @@
         <v>45146</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49679,7 +49679,7 @@
         <v>45068</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49752,7 +49752,7 @@
         <v>45305</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49825,7 +49825,7 @@
         <v>44574</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49903,7 +49903,7 @@
         <v>45259</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49976,7 +49976,7 @@
         <v>45352</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50049,7 +50049,7 @@
         <v>44608</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50122,7 +50122,7 @@
         <v>45261</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50195,7 +50195,7 @@
         <v>44636</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50268,7 +50268,7 @@
         <v>45370</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50341,7 +50341,7 @@
         <v>44489</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50419,7 +50419,7 @@
         <v>45356</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50492,7 +50492,7 @@
         <v>45330</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50565,7 +50565,7 @@
         <v>45349</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50638,7 +50638,7 @@
         <v>45352</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50711,7 +50711,7 @@
         <v>45435</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50784,7 +50784,7 @@
         <v>45370</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50857,7 +50857,7 @@
         <v>45580</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45370</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51003,7 +51003,7 @@
         <v>45335</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>45534</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51149,7 +51149,7 @@
         <v>44967</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51222,7 +51222,7 @@
         <v>45352</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51295,7 +51295,7 @@
         <v>44489</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51373,7 +51373,7 @@
         <v>45744</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51446,7 +51446,7 @@
         <v>45744</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51519,7 +51519,7 @@
         <v>45750</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51592,7 +51592,7 @@
         <v>45756</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51665,7 +51665,7 @@
         <v>45715</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51738,7 +51738,7 @@
         <v>45910</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51811,7 +51811,7 @@
         <v>46020</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51884,7 +51884,7 @@
         <v>46042</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51957,7 +51957,7 @@
         <v>46058</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52030,7 +52030,7 @@
         <v>46122</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52103,7 +52103,7 @@
         <v>46154</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52176,7 +52176,7 @@
         <v>46154</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52249,7 +52249,7 @@
         <v>46154</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52322,7 +52322,7 @@
         <v>46154</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52395,7 +52395,7 @@
         <v>46160</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52468,7 +52468,7 @@
         <v>46206</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52541,7 +52541,7 @@
         <v>46253</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52619,7 +52619,7 @@
         <v>46308</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>

--- a/Översikt FALKENBERG.xlsx
+++ b/Översikt FALKENBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46247</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>46253</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>46255</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45560</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>46255</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45741</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>46282</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>44592</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>44593</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>44628</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>44516</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>45079</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>45356</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>45527</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>45680</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45795</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>45335</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>45600</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>45456</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>44616</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44539</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>45356</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>44818</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44507</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>44517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>45565</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>45914</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>45561</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>45196</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>45667</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>45273</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>45068</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>45273</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>46248</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>44946</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         <v>44926</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>45355</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>45600</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>44972</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>45239</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>44902</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>44705</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>44964</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>45352</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>45352</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>45349</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>45330</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>45945</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>46099</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44806</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>44607</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>44553</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>44539</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>44868</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>44867</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44680</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44600</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44868</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>44816</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>44613</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>44689</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>44616</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>44616</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>44617</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>44547</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44599</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>44879</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44711</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44544</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>44600</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>44692</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>44692</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>44600</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>44539</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>44539</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>44747</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>44813</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>44841</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>44545</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>44719</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>44866</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>44593</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>44803</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>44614</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>44685</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>44596</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>44638</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>44539</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>44537</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>44628</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>44543</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>44539</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>45888</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>44908</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>44539</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>45782</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>45582</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>45627</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>45705</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>45350</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>45580</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>45800</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>45212</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>45212</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>45345</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>45889</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>45377</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>45770</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>45174</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>45195</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>45895</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>45189</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>45895</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         <v>44946</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>44946</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>45357</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>44974</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>45400</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>45566</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>44806</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>44517</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
         <v>45188</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11388,7 +11388,7 @@
         <v>45182</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>45772</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11534,7 +11534,7 @@
         <v>45391</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         <v>45901</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>45901</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>45670</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>45381</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>45384</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11972,7 +11972,7 @@
         <v>45908</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>45363</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>45036</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>46162</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>45482</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>45435</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>44984</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>45435</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>46162</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>45914</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>46164</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         <v>46164</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>45917</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>46164</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>45363</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>45076</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13140,7 +13140,7 @@
         <v>45923</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>45924</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>45923</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>46166</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>45923</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>45923</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>44806</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>45926</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
         <v>45926</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13797,7 +13797,7 @@
         <v>45926</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13870,7 +13870,7 @@
         <v>45926</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>44574</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>46168</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>46172</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>45931</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>45931</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>45931</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>46170</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>45546</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>45896</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>45896</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>45252</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>45601</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14824,7 +14824,7 @@
         <v>45937</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>45323</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>45624</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>44652</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
         <v>45940</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>45681</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>45682</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15340,7 +15340,7 @@
         <v>45682</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>45246</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>45673</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>45321</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         <v>45426</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
         <v>46007</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>45229</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         <v>45946</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>45946</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>45946</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>45357</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         <v>45127</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>45546</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>45462</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>44985</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
         <v>45950</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16518,7 +16518,7 @@
         <v>45548</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>46178</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>45435</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>45952</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45951</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>46182</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>45044</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>45952</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>45952</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>44631</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>46182</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>45953</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>45953</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>44689</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17540,7 +17540,7 @@
         <v>45954</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>46184</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>44687</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>45702</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>45959</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>45950</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         <v>45960</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>46184</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>45266</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18202,7 +18202,7 @@
         <v>45959</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>45959</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>45664</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>45959</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>45629</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>45960</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>45964</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>44903</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18791,7 +18791,7 @@
         <v>45961</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>45965</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>45965</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>45965</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>44642</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>45965</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>45686</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>45965</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>45965</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>45965</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>45552</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>45351</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>45968</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>46190</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>44846</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>45968</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>45324</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>45971</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>45419</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45243</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20251,7 +20251,7 @@
         <v>45971</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>45971</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>45120</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20470,7 +20470,7 @@
         <v>45971</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>45037</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>44986</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>45973</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>45681</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20840,7 +20840,7 @@
         <v>46196</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20913,7 +20913,7 @@
         <v>45973</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>45975</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>44963</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21137,7 +21137,7 @@
         <v>44963</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         <v>46200</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>44903</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>46203</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>46202</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>45219</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44938</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>46202</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         <v>46202</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>46203</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>45323</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>44957</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>45029</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>44986</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45001</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45616</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>45667</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45978</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>45989</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>46211</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>45127</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22685,7 +22685,7 @@
         <v>45580</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>45147</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>46212</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>46212</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>46217</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>45226</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>45681</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>45300</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>44622</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>45999</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>45667</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>45777</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>46225</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23634,7 +23634,7 @@
         <v>46003</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         <v>45782</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>46006</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>46004</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>45278</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>45785</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>45244</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>46204</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>45953</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>45741</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>45443</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>45790</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>46282</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>45562</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>46282</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>45582</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>46281</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24875,7 +24875,7 @@
         <v>46282</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24948,7 +24948,7 @@
         <v>46282</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25021,7 +25021,7 @@
         <v>45533</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25094,7 +25094,7 @@
         <v>45439</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>46244</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>45616</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25313,7 +25313,7 @@
         <v>46035</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25386,7 +25386,7 @@
         <v>45686</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>46037</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>46037</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>45666</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>45748</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         <v>44545</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>46042</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25902,7 +25902,7 @@
         <v>46045</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25975,7 +25975,7 @@
         <v>45799</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26048,7 +26048,7 @@
         <v>45799</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>46041</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>45799</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>46049</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26340,7 +26340,7 @@
         <v>46052</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>45247</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>46290</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26559,7 +26559,7 @@
         <v>46289</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26632,7 +26632,7 @@
         <v>46055</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>46282</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
         <v>45966</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26851,7 +26851,7 @@
         <v>45810</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26924,7 +26924,7 @@
         <v>45274</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26997,7 +26997,7 @@
         <v>46294</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27070,7 +27070,7 @@
         <v>45342</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27148,7 +27148,7 @@
         <v>46293</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>46248</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27294,7 +27294,7 @@
         <v>46293</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27367,7 +27367,7 @@
         <v>46293</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>45467</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>45615</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27586,7 +27586,7 @@
         <v>45712</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>46065</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27732,7 +27732,7 @@
         <v>46293</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>45630</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27878,7 +27878,7 @@
         <v>45300</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27951,7 +27951,7 @@
         <v>45300</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28024,7 +28024,7 @@
         <v>45300</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>46070</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28170,7 +28170,7 @@
         <v>46069</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>44946</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28316,7 +28316,7 @@
         <v>46296</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28389,7 +28389,7 @@
         <v>46253</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28462,7 +28462,7 @@
         <v>45821</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28535,7 +28535,7 @@
         <v>46077</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>46251</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28681,7 +28681,7 @@
         <v>46295</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28754,7 +28754,7 @@
         <v>46082</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28827,7 +28827,7 @@
         <v>46065</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>46082</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         <v>45834</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29046,7 +29046,7 @@
         <v>45834</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29119,7 +29119,7 @@
         <v>46087</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29192,7 +29192,7 @@
         <v>45834</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29265,7 +29265,7 @@
         <v>45838</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>45838</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29411,7 +29411,7 @@
         <v>45838</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29484,7 +29484,7 @@
         <v>45838</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>45838</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29630,7 +29630,7 @@
         <v>46097</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>45441</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>44984</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29854,7 +29854,7 @@
         <v>45845</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>46259</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30000,7 +30000,7 @@
         <v>46259</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>46259</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         <v>46258</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>45848</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30292,7 +30292,7 @@
         <v>46106</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>46106</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30438,7 +30438,7 @@
         <v>45644</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>46302</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30584,7 +30584,7 @@
         <v>45750</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30657,7 +30657,7 @@
         <v>46304</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30730,7 +30730,7 @@
         <v>45800</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30803,7 +30803,7 @@
         <v>46304</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>46304</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30949,7 +30949,7 @@
         <v>45777</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>46120</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31100,7 +31100,7 @@
         <v>44515</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31173,7 +31173,7 @@
         <v>44521</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31246,7 +31246,7 @@
         <v>45422</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>45422</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31402,7 +31402,7 @@
         <v>45422</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>44818</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>45068</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>44866</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>45387</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>45434</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>45229</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31923,7 +31923,7 @@
         <v>45273</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>45079</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>45305</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32142,7 +32142,7 @@
         <v>44693</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>44952</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>45817</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32361,7 +32361,7 @@
         <v>45146</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>45840</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32512,7 +32512,7 @@
         <v>45337</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32585,7 +32585,7 @@
         <v>44952</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32658,7 +32658,7 @@
         <v>45761</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>45280</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32804,7 +32804,7 @@
         <v>45337</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>45068</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32950,7 +32950,7 @@
         <v>45074</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>45270</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>45249</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33169,7 +33169,7 @@
         <v>44846</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>45013</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33315,7 +33315,7 @@
         <v>44846</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33388,7 +33388,7 @@
         <v>45260</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>45248</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>45249</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33612,7 +33612,7 @@
         <v>45271</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>45434</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>45215</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>44767</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>45013</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>45754</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>44502</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>45826</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34196,7 +34196,7 @@
         <v>45249</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>45250</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>45243</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34415,7 +34415,7 @@
         <v>44943</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>44943</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>46127</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>45184</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>45184</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>45184</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34863,7 +34863,7 @@
         <v>44602</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>46260</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>46307</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>46307</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>45071</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44897</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>45329</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35374,7 +35374,7 @@
         <v>45524</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35447,7 +35447,7 @@
         <v>44916</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35520,7 +35520,7 @@
         <v>44576</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35593,7 +35593,7 @@
         <v>44900</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>45770</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35744,7 +35744,7 @@
         <v>46293</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>44584</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35890,7 +35890,7 @@
         <v>45272</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>46310</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>45554</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36109,7 +36109,7 @@
         <v>46293</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>45349</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>46310</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>45831</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36401,7 +36401,7 @@
         <v>45390</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>45219</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>45764</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36620,7 +36620,7 @@
         <v>45856</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36693,7 +36693,7 @@
         <v>45709</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36766,7 +36766,7 @@
         <v>45547</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>46263</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>46304</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>45350</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>45811</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>45552</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>45355</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37277,7 +37277,7 @@
         <v>44938</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>46271</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37423,7 +37423,7 @@
         <v>46271</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37496,7 +37496,7 @@
         <v>45842</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37569,7 +37569,7 @@
         <v>45561</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>46272</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>46316</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>45555</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>44600</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>46272</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38012,7 +38012,7 @@
         <v>44974</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>45246</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38158,7 +38158,7 @@
         <v>45575</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>46263</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38304,7 +38304,7 @@
         <v>46307</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38377,7 +38377,7 @@
         <v>44656</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38450,7 +38450,7 @@
         <v>44694</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38523,7 +38523,7 @@
         <v>46142</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38596,7 +38596,7 @@
         <v>46087</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38669,7 +38669,7 @@
         <v>46142</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38742,7 +38742,7 @@
         <v>44610</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>45055</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38888,7 +38888,7 @@
         <v>45055</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38961,7 +38961,7 @@
         <v>45575</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39034,7 +39034,7 @@
         <v>45273</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39107,7 +39107,7 @@
         <v>45741</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39180,7 +39180,7 @@
         <v>45266</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39253,7 +39253,7 @@
         <v>45635</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39326,7 +39326,7 @@
         <v>45933</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>45959</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>45959</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>45581</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>45714</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>44946</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39764,7 +39764,7 @@
         <v>45667</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39842,7 +39842,7 @@
         <v>45202</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39915,7 +39915,7 @@
         <v>45058</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39988,7 +39988,7 @@
         <v>45015</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40061,7 +40061,7 @@
         <v>45084</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40134,7 +40134,7 @@
         <v>44964</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40207,7 +40207,7 @@
         <v>45474</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40280,7 +40280,7 @@
         <v>44977</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40358,7 +40358,7 @@
         <v>45035</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40431,7 +40431,7 @@
         <v>45582</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>45595</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40577,7 +40577,7 @@
         <v>45187</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40650,7 +40650,7 @@
         <v>45174</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>45152</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40796,7 +40796,7 @@
         <v>44986</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40869,7 +40869,7 @@
         <v>45174</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40942,7 +40942,7 @@
         <v>45174</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41015,7 +41015,7 @@
         <v>45189</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>44852</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>44524</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>45714</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>45736</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         <v>45035</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>45751</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41531,7 +41531,7 @@
         <v>45226</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>44827</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>45205</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>45201</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41828,7 +41828,7 @@
         <v>44740</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>44740</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41974,7 +41974,7 @@
         <v>45566</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>45245</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42120,7 +42120,7 @@
         <v>44910</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42193,7 +42193,7 @@
         <v>44910</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42266,7 +42266,7 @@
         <v>45068</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42339,7 +42339,7 @@
         <v>45735</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42412,7 +42412,7 @@
         <v>45628</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>45232</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42563,7 +42563,7 @@
         <v>44893</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>45001</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>45751</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
         <v>45119</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>44882</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45456</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>44957</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43074,7 +43074,7 @@
         <v>44538</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>45188</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>44966</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45350</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>45280</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>44545</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         <v>45597</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43590,7 +43590,7 @@
         <v>45117</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>44999</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43736,7 +43736,7 @@
         <v>45131</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43809,7 +43809,7 @@
         <v>45142</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>45239</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45425</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>45474</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>44525</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44174,7 +44174,7 @@
         <v>44543</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>45019</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>44827</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>45138</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>44974</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44539,7 +44539,7 @@
         <v>44848</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45566</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>45566</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>45566</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>45105</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>45048</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>45148</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>45328</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45128,7 +45128,7 @@
         <v>44986</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45201,7 +45201,7 @@
         <v>44622</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45274,7 +45274,7 @@
         <v>45714</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45347,7 +45347,7 @@
         <v>45481</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45377</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>45552</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45566,7 +45566,7 @@
         <v>45678</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45639,7 +45639,7 @@
         <v>45401</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45714</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45790,7 +45790,7 @@
         <v>45588</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45667</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>44644</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>45190</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>44554</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46155,7 +46155,7 @@
         <v>45601</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46228,7 +46228,7 @@
         <v>45435</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46301,7 +46301,7 @@
         <v>45618</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46374,7 +46374,7 @@
         <v>45643</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>45182</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>45751</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45187</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>45401</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45435</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46822,7 +46822,7 @@
         <v>45414</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>44811</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46973,7 +46973,7 @@
         <v>45188</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47046,7 +47046,7 @@
         <v>45181</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47119,7 +47119,7 @@
         <v>44664</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47192,7 +47192,7 @@
         <v>45680</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47265,7 +47265,7 @@
         <v>45163</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47338,7 +47338,7 @@
         <v>45182</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47411,7 +47411,7 @@
         <v>45188</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47484,7 +47484,7 @@
         <v>45131</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47557,7 +47557,7 @@
         <v>45239</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47630,7 +47630,7 @@
         <v>45300</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47703,7 +47703,7 @@
         <v>45328</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>45762</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47854,7 +47854,7 @@
         <v>45343</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>44627</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>45272</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48073,7 +48073,7 @@
         <v>44958</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45091</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48224,7 +48224,7 @@
         <v>45118</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48297,7 +48297,7 @@
         <v>45252</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>44785</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48443,7 +48443,7 @@
         <v>45282</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48516,7 +48516,7 @@
         <v>44831</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45357</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45091</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>45539</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48808,7 +48808,7 @@
         <v>45238</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48881,7 +48881,7 @@
         <v>45691</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>44946</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49027,7 +49027,7 @@
         <v>45044</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49100,7 +49100,7 @@
         <v>45618</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>45618</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49246,7 +49246,7 @@
         <v>45326</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49319,7 +49319,7 @@
         <v>44946</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49392,7 +49392,7 @@
         <v>44627</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49465,7 +49465,7 @@
         <v>44887</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49538,7 +49538,7 @@
         <v>44692</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49611,7 +49611,7 @@
         <v>45560</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49684,7 +49684,7 @@
         <v>45211</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49757,7 +49757,7 @@
         <v>45175</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49830,7 +49830,7 @@
         <v>44970</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49903,7 +49903,7 @@
         <v>44574</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49981,7 +49981,7 @@
         <v>44608</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50054,7 +50054,7 @@
         <v>44636</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45259</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50200,7 +50200,7 @@
         <v>45352</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50273,7 +50273,7 @@
         <v>45261</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50346,7 +50346,7 @@
         <v>45370</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50419,7 +50419,7 @@
         <v>45356</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50492,7 +50492,7 @@
         <v>45330</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50565,7 +50565,7 @@
         <v>45349</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50638,7 +50638,7 @@
         <v>45352</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50711,7 +50711,7 @@
         <v>45435</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50784,7 +50784,7 @@
         <v>45370</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50857,7 +50857,7 @@
         <v>45580</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45370</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51003,7 +51003,7 @@
         <v>45335</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>45534</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51149,7 +51149,7 @@
         <v>44967</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51222,7 +51222,7 @@
         <v>45352</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51295,7 +51295,7 @@
         <v>45744</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51368,7 +51368,7 @@
         <v>45744</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51441,7 +51441,7 @@
         <v>45750</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51514,7 +51514,7 @@
         <v>45756</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51587,7 +51587,7 @@
         <v>45715</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51660,7 +51660,7 @@
         <v>45910</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51733,7 +51733,7 @@
         <v>46020</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51806,7 +51806,7 @@
         <v>46042</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51879,7 +51879,7 @@
         <v>46058</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51952,7 +51952,7 @@
         <v>46122</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52025,7 +52025,7 @@
         <v>46154</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52098,7 +52098,7 @@
         <v>46154</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52171,7 +52171,7 @@
         <v>46154</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52244,7 +52244,7 @@
         <v>46154</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52317,7 +52317,7 @@
         <v>46160</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52390,7 +52390,7 @@
         <v>46206</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52463,7 +52463,7 @@
         <v>46253</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52541,7 +52541,7 @@
         <v>46308</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>

--- a/Översikt FALKENBERG.xlsx
+++ b/Översikt FALKENBERG.xlsx
@@ -601,7 +601,7 @@
         <v>46247</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>46253</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>46255</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44593</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45560</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>46255</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45741</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>46282</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>44592</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>44593</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>44628</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>44516</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>45079</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>45356</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>45527</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>45680</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45795</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>45335</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>45600</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>45456</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>44616</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44539</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>45356</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>44818</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44507</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>44517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>45565</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>45914</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>45561</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>45196</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>45667</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>45273</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>45068</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>45273</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>46248</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>44946</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         <v>44926</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>45355</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>45600</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>44972</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>45239</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>44902</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>44705</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>44964</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>45352</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>45352</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>45349</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>45330</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>45945</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>46099</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>44806</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>44607</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>44553</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>44539</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>44868</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>44867</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44680</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44600</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44868</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>44816</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>44613</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>44689</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>44616</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>44616</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>44617</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>44547</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44599</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>44879</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44711</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44544</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>44600</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>44692</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>44692</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>44600</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>44539</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>44539</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>44747</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>44813</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>44841</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>44545</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>44719</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>44866</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>44593</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>44803</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>44614</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>44685</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>44596</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>44638</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>44539</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>44537</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>44628</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>44543</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>44539</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>45888</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>44908</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>44539</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>45782</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>45582</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>45627</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>45705</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>45350</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>45580</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>45800</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>45212</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>45212</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>45345</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>45889</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>45377</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>45770</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>45174</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>45195</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>45895</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>45189</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>45895</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         <v>44946</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>44946</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>45357</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>44974</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>45400</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>45566</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>44806</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>44517</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
         <v>45188</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11388,7 +11388,7 @@
         <v>45182</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>45772</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11534,7 +11534,7 @@
         <v>45391</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         <v>45901</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>45901</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>45670</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>45381</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>45384</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11972,7 +11972,7 @@
         <v>45908</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>45363</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>45036</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>46162</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>45482</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>45435</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>44984</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>45435</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>46162</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>45914</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>46164</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         <v>46164</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>45917</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>46164</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>45363</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>45076</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13140,7 +13140,7 @@
         <v>45923</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>45924</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>45923</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>46166</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>45923</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>45923</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>44806</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>45926</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
         <v>45926</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13797,7 +13797,7 @@
         <v>45926</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13870,7 +13870,7 @@
         <v>45926</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>44574</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>46168</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>46172</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>45931</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>45931</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>45931</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>46170</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>45546</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>45896</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>45896</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>45252</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>45601</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14824,7 +14824,7 @@
         <v>45937</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>45323</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>45624</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>44652</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
         <v>45940</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>45681</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>45682</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15340,7 +15340,7 @@
         <v>45682</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>45246</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>45673</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>45321</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         <v>45426</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
         <v>46007</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>45229</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         <v>45946</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>45946</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>45946</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>45357</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         <v>45127</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>45546</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>45462</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>44985</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
         <v>45950</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16518,7 +16518,7 @@
         <v>45548</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>46178</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>45435</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>45952</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45951</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>46182</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>45044</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>45952</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>45952</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>44631</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>46182</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>45953</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>45953</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>44689</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17540,7 +17540,7 @@
         <v>45954</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>46184</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>44687</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>45702</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>45959</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>45950</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         <v>45960</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>46184</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>45266</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18202,7 +18202,7 @@
         <v>45959</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>45959</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>45664</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>45959</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>45629</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>45960</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>45964</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>44903</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18791,7 +18791,7 @@
         <v>45961</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>45965</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>45965</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>45965</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>44642</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>45965</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>45686</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>45965</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>45965</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>45965</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>45552</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>45351</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>45968</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>46190</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>44846</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>45968</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>45324</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>45971</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>45419</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45243</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20251,7 +20251,7 @@
         <v>45971</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>45971</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>45120</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20470,7 +20470,7 @@
         <v>45971</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>45037</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>44986</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>45973</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>45681</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20840,7 +20840,7 @@
         <v>46196</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20913,7 +20913,7 @@
         <v>45973</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>45975</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>44963</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21137,7 +21137,7 @@
         <v>44963</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         <v>46200</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>44903</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>46203</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>46202</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>45219</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44938</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>46202</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         <v>46202</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>46203</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>45323</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>44957</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>45029</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>44986</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45001</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45616</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>45667</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45978</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>45989</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>46211</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>45127</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22685,7 +22685,7 @@
         <v>45580</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>45147</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>46212</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>46212</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>46217</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>45226</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>45681</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>45300</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>44622</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>45999</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>45667</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>45777</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>46225</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23634,7 +23634,7 @@
         <v>46003</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         <v>45782</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>46006</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>46004</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>45278</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>45785</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>45244</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>46204</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>45953</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>45741</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>45443</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>45790</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>46282</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>45562</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>46282</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>45582</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>46281</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24875,7 +24875,7 @@
         <v>46282</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24948,7 +24948,7 @@
         <v>46282</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25021,7 +25021,7 @@
         <v>45533</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25094,7 +25094,7 @@
         <v>45439</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>46244</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>45616</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25313,7 +25313,7 @@
         <v>46035</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25386,7 +25386,7 @@
         <v>45686</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>46037</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>46037</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>45666</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>45748</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         <v>44545</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>46042</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25902,7 +25902,7 @@
         <v>46045</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25975,7 +25975,7 @@
         <v>45799</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26048,7 +26048,7 @@
         <v>45799</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>46041</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>45799</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>46049</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26340,7 +26340,7 @@
         <v>46052</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>45247</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>46290</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26559,7 +26559,7 @@
         <v>46289</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26632,7 +26632,7 @@
         <v>46055</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>46282</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
         <v>45966</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26851,7 +26851,7 @@
         <v>45810</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26924,7 +26924,7 @@
         <v>45274</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26997,7 +26997,7 @@
         <v>46294</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27070,7 +27070,7 @@
         <v>45342</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27148,7 +27148,7 @@
         <v>46293</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>46248</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27294,7 +27294,7 @@
         <v>46293</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27367,7 +27367,7 @@
         <v>46293</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>45467</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>45615</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27586,7 +27586,7 @@
         <v>45712</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>46065</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27732,7 +27732,7 @@
         <v>46293</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>45630</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27878,7 +27878,7 @@
         <v>45300</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27951,7 +27951,7 @@
         <v>45300</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28024,7 +28024,7 @@
         <v>45300</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>46070</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28170,7 +28170,7 @@
         <v>46069</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>44946</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28316,7 +28316,7 @@
         <v>46296</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28389,7 +28389,7 @@
         <v>46253</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28462,7 +28462,7 @@
         <v>45821</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28535,7 +28535,7 @@
         <v>46077</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>46251</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28681,7 +28681,7 @@
         <v>46295</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28754,7 +28754,7 @@
         <v>46082</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28827,7 +28827,7 @@
         <v>46065</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>46082</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         <v>45834</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29046,7 +29046,7 @@
         <v>45834</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29119,7 +29119,7 @@
         <v>46087</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29192,7 +29192,7 @@
         <v>45834</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29265,7 +29265,7 @@
         <v>45838</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>45838</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29411,7 +29411,7 @@
         <v>45838</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29484,7 +29484,7 @@
         <v>45838</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>45838</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29630,7 +29630,7 @@
         <v>46097</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>45441</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>44984</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29854,7 +29854,7 @@
         <v>45845</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>46259</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30000,7 +30000,7 @@
         <v>46259</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>46259</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         <v>46258</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>45848</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30292,7 +30292,7 @@
         <v>46106</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>46106</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30438,7 +30438,7 @@
         <v>45644</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>46302</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30584,7 +30584,7 @@
         <v>45750</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30657,7 +30657,7 @@
         <v>46304</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30730,7 +30730,7 @@
         <v>45800</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30803,7 +30803,7 @@
         <v>46304</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>46304</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30949,7 +30949,7 @@
         <v>45777</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>46120</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31100,7 +31100,7 @@
         <v>44515</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31173,7 +31173,7 @@
         <v>44521</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31246,7 +31246,7 @@
         <v>45422</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>45422</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31402,7 +31402,7 @@
         <v>45422</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>44818</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>45068</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>44866</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>45387</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>45434</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>45229</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31923,7 +31923,7 @@
         <v>45273</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>45079</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>45305</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32142,7 +32142,7 @@
         <v>44693</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>44952</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>45817</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32361,7 +32361,7 @@
         <v>45146</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>45840</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32512,7 +32512,7 @@
         <v>45337</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32585,7 +32585,7 @@
         <v>44952</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32658,7 +32658,7 @@
         <v>45761</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>45280</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32804,7 +32804,7 @@
         <v>45337</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>45068</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32950,7 +32950,7 @@
         <v>45074</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>45270</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>45249</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33169,7 +33169,7 @@
         <v>44846</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>45013</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33315,7 +33315,7 @@
         <v>44846</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33388,7 +33388,7 @@
         <v>45260</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>45248</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>45249</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33612,7 +33612,7 @@
         <v>45271</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>45434</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>45215</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>44767</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>45013</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>45754</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>44502</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>45826</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34196,7 +34196,7 @@
         <v>45249</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>45250</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>45243</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34415,7 +34415,7 @@
         <v>44943</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>44943</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>46127</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>45184</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>45184</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>45184</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34863,7 +34863,7 @@
         <v>44602</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>46260</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>46307</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>46307</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>45071</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44897</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>45329</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35374,7 +35374,7 @@
         <v>45524</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35447,7 +35447,7 @@
         <v>44916</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35520,7 +35520,7 @@
         <v>44576</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35593,7 +35593,7 @@
         <v>44900</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>45770</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35744,7 +35744,7 @@
         <v>46293</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>44584</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35890,7 +35890,7 @@
         <v>45272</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>46310</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>45554</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36109,7 +36109,7 @@
         <v>46293</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>45349</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>46310</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>45831</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36401,7 +36401,7 @@
         <v>45390</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>45219</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>45764</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36620,7 +36620,7 @@
         <v>45856</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36693,7 +36693,7 @@
         <v>45709</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36766,7 +36766,7 @@
         <v>45547</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>46263</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>46304</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>45350</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>45811</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>45552</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>45355</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37277,7 +37277,7 @@
         <v>44938</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>46271</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37423,7 +37423,7 @@
         <v>46271</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37496,7 +37496,7 @@
         <v>45842</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37569,7 +37569,7 @@
         <v>45561</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>46272</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>46316</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>45555</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>44600</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>46272</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38012,7 +38012,7 @@
         <v>44974</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>45246</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38158,7 +38158,7 @@
         <v>45575</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>46263</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38304,7 +38304,7 @@
         <v>46307</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38377,7 +38377,7 @@
         <v>44656</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38450,7 +38450,7 @@
         <v>44694</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38523,7 +38523,7 @@
         <v>46142</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38596,7 +38596,7 @@
         <v>46087</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38669,7 +38669,7 @@
         <v>46142</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38742,7 +38742,7 @@
         <v>44610</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>45055</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38888,7 +38888,7 @@
         <v>45055</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38961,7 +38961,7 @@
         <v>45575</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39034,7 +39034,7 @@
         <v>45273</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39107,7 +39107,7 @@
         <v>45741</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39180,7 +39180,7 @@
         <v>45266</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39253,7 +39253,7 @@
         <v>45635</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39326,7 +39326,7 @@
         <v>45933</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>45959</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>45959</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>45581</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>45714</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>44946</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39764,7 +39764,7 @@
         <v>45667</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39842,7 +39842,7 @@
         <v>45202</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39915,7 +39915,7 @@
         <v>45058</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39988,7 +39988,7 @@
         <v>45015</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40061,7 +40061,7 @@
         <v>45084</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40134,7 +40134,7 @@
         <v>44964</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40207,7 +40207,7 @@
         <v>45474</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40280,7 +40280,7 @@
         <v>44977</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40358,7 +40358,7 @@
         <v>45035</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40431,7 +40431,7 @@
         <v>45582</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>45595</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40577,7 +40577,7 @@
         <v>45187</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40650,7 +40650,7 @@
         <v>45174</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>45152</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40796,7 +40796,7 @@
         <v>44986</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40869,7 +40869,7 @@
         <v>45174</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40942,7 +40942,7 @@
         <v>45174</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41015,7 +41015,7 @@
         <v>45189</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>44852</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>44524</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>45714</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>45736</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         <v>45035</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>45751</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41531,7 +41531,7 @@
         <v>45226</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>44827</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>45205</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>45201</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41828,7 +41828,7 @@
         <v>44740</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41901,7 +41901,7 @@
         <v>44740</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41974,7 +41974,7 @@
         <v>45566</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>45245</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42120,7 +42120,7 @@
         <v>44910</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42193,7 +42193,7 @@
         <v>44910</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42266,7 +42266,7 @@
         <v>45068</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42339,7 +42339,7 @@
         <v>45735</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42412,7 +42412,7 @@
         <v>45628</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>45232</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42563,7 +42563,7 @@
         <v>44893</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>45001</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>45751</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
         <v>45119</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>44882</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45456</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>44957</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43074,7 +43074,7 @@
         <v>44538</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>45188</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>44966</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45350</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>45280</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>44545</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         <v>45597</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43590,7 +43590,7 @@
         <v>45117</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>44999</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43736,7 +43736,7 @@
         <v>45131</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43809,7 +43809,7 @@
         <v>45142</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>45239</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45425</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>45474</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>44525</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44174,7 +44174,7 @@
         <v>44543</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>45019</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>44827</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>45138</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>44974</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44539,7 +44539,7 @@
         <v>44848</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45566</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>45566</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>45566</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>45105</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>45048</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>45148</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>45328</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45128,7 +45128,7 @@
         <v>44986</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45201,7 +45201,7 @@
         <v>44622</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45274,7 +45274,7 @@
         <v>45714</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45347,7 +45347,7 @@
         <v>45481</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45377</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>45552</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45566,7 +45566,7 @@
         <v>45678</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45639,7 +45639,7 @@
         <v>45401</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45714</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45790,7 +45790,7 @@
         <v>45588</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45667</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>44644</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>45190</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
         <v>44554</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46155,7 +46155,7 @@
         <v>45601</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46228,7 +46228,7 @@
         <v>45435</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46301,7 +46301,7 @@
         <v>45618</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46374,7 +46374,7 @@
         <v>45643</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>45182</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>45751</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45187</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>45401</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45435</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46822,7 +46822,7 @@
         <v>45414</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>44811</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46973,7 +46973,7 @@
         <v>45188</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47046,7 +47046,7 @@
         <v>45181</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47119,7 +47119,7 @@
         <v>44664</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47192,7 +47192,7 @@
         <v>45680</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47265,7 +47265,7 @@
         <v>45163</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47338,7 +47338,7 @@
         <v>45182</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47411,7 +47411,7 @@
         <v>45188</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47484,7 +47484,7 @@
         <v>45131</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47557,7 +47557,7 @@
         <v>45239</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47630,7 +47630,7 @@
         <v>45300</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47703,7 +47703,7 @@
         <v>45328</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>45762</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47854,7 +47854,7 @@
         <v>45343</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>44627</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>45272</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48073,7 +48073,7 @@
         <v>44958</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45091</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48224,7 +48224,7 @@
         <v>45118</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48297,7 +48297,7 @@
         <v>45252</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>44785</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48443,7 +48443,7 @@
         <v>45282</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48516,7 +48516,7 @@
         <v>44831</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45357</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45091</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>45539</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48808,7 +48808,7 @@
         <v>45238</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48881,7 +48881,7 @@
         <v>45691</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>44946</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49027,7 +49027,7 @@
         <v>45044</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49100,7 +49100,7 @@
         <v>45618</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>45618</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49246,7 +49246,7 @@
         <v>45326</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49319,7 +49319,7 @@
         <v>44946</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49392,7 +49392,7 @@
         <v>44627</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49465,7 +49465,7 @@
         <v>44887</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49538,7 +49538,7 @@
         <v>44692</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49611,7 +49611,7 @@
         <v>45560</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49684,7 +49684,7 @@
         <v>45211</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49757,7 +49757,7 @@
         <v>45175</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49830,7 +49830,7 @@
         <v>44970</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49903,7 +49903,7 @@
         <v>44574</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49981,7 +49981,7 @@
         <v>44608</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50054,7 +50054,7 @@
         <v>44636</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45259</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50200,7 +50200,7 @@
         <v>45352</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50273,7 +50273,7 @@
         <v>45261</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50346,7 +50346,7 @@
         <v>45370</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50419,7 +50419,7 @@
         <v>45356</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50492,7 +50492,7 @@
         <v>45330</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50565,7 +50565,7 @@
         <v>45349</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50638,7 +50638,7 @@
         <v>45352</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50711,7 +50711,7 @@
         <v>45435</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50784,7 +50784,7 @@
         <v>45370</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50857,7 +50857,7 @@
         <v>45580</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45370</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51003,7 +51003,7 @@
         <v>45335</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>45534</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51149,7 +51149,7 @@
         <v>44967</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51222,7 +51222,7 @@
         <v>45352</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51295,7 +51295,7 @@
         <v>45744</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51368,7 +51368,7 @@
         <v>45744</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51441,7 +51441,7 @@
         <v>45750</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51514,7 +51514,7 @@
         <v>45756</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51587,7 +51587,7 @@
         <v>45715</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51660,7 +51660,7 @@
         <v>45910</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51733,7 +51733,7 @@
         <v>46020</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51806,7 +51806,7 @@
         <v>46042</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51879,7 +51879,7 @@
         <v>46058</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51952,7 +51952,7 @@
         <v>46122</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52025,7 +52025,7 @@
         <v>46154</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52098,7 +52098,7 @@
         <v>46154</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52171,7 +52171,7 @@
         <v>46154</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52244,7 +52244,7 @@
         <v>46154</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52317,7 +52317,7 @@
         <v>46160</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52390,7 +52390,7 @@
         <v>46206</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52463,7 +52463,7 @@
         <v>46253</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52541,7 +52541,7 @@
         <v>46308</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
